--- a/Replication Package/Evaluation/test_dataset.xlsx
+++ b/Replication Package/Evaluation/test_dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\issue_analyzing_tool\Replication Package\Evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB1DE64A-C055-4EF2-A6F6-7FC2E653F38C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{911AE6BE-4CE2-495D-8B68-849EEB4D3077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-7725" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="510">
   <si>
     <t>Language</t>
   </si>
@@ -195,7 +195,7 @@
     <t>['Scaffold']</t>
   </si>
   <si>
-    <t>['run_config_hooks', 'invalid_hook', 'cfg', 'create_run', 'get_config_modifications', 'test_config_hook_updates_config', 'hook', 'foo', 'test_option_hooks_without_options_arg_raises']</t>
+    <t>['cfg', 'test_config_hook_updates_config', 'create_run', 'hook', 'run_config_hooks', 'get_config_modifications', 'foo', 'test_option_hooks_without_options_arg_raises', 'invalid_hook']</t>
   </si>
   <si>
     <t>[105, 111, 385, 386, 387, 257, 258, 259, 260, 261, 262, 263, 264, 265, 266, 267, 268, 269, 270, 271, 272, 273, 274, 275]</t>
@@ -245,13 +245,13 @@
     <t>https://github.com/IDSIA/sacred/issues/329</t>
   </si>
   <si>
-    <t>['tests/test_observers/test_file_storage_observer.py', 'sacred/observers/file_storage.py']</t>
+    <t>['sacred/observers/file_storage.py', 'tests/test_observers/test_file_storage_observer.py']</t>
   </si>
   <si>
     <t>['FileStorageObserver']</t>
   </si>
   <si>
-    <t>['create', 'test_fs_observer_create_does_not_create_basedir', 'dir_obs', 'test_fs_observer_started_event_creates_rundir', 'sample_run', 'tmpfile', 'started_event', 'test_fs_observer_queued_event_creates_rundir', 'queued_event']</t>
+    <t>['queued_event', 'tmpfile', 'dir_obs', 'create', 'started_event', 'sample_run', 'test_fs_observer_started_event_creates_rundir', 'test_fs_observer_queued_event_creates_rundir', 'test_fs_observer_create_does_not_create_basedir']</t>
   </si>
   <si>
     <t>[55, 56, 93, 94, 41, 42, 66, 67, 68, 69, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79, 80, 81, 82, 83, 84, 85, 86, 87, 88, 89, 90, 91, 92, 93]</t>
@@ -312,7 +312,7 @@
     <t>[]</t>
   </si>
   <si>
-    <t>['is_subdir', 'filtered_traceback_format', 'print_filtered_stacktrace']</t>
+    <t>['filtered_traceback_format', 'print_filtered_stacktrace', 'is_subdir']</t>
   </si>
   <si>
     <t>[262, 263, 264, 265, 267, 268, 269, 270, 271, 272, 273, 274, 275, 276, 277, 278, 279, 280, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 297, 298, 299, 300, 301, 302, 303, 304, 305, 306, 307, 308, 309, 310, 311]</t>
@@ -337,7 +337,7 @@
     <t>https://github.com/IDSIA/sacred/issues/289</t>
   </si>
   <si>
-    <t>['sacred/stdout_capturing.py', 'sacred/observers/file_storage.py', 'tests/test_run.py']</t>
+    <t>['sacred/observers/file_storage.py', 'tests/test_run.py', 'sacred/stdout_capturing.py']</t>
   </si>
   <si>
     <t>['tee_output_fd', 'test_captured_out_filter']</t>
@@ -478,7 +478,7 @@
     <t>https://github.com/PyPSA/PyPSA/issues/592</t>
   </si>
   <si>
-    <t>['pypsa/optimization/constraints.py', 'pypsa/linopf.py']</t>
+    <t>['pypsa/linopf.py', 'pypsa/optimization/constraints.py']</t>
   </si>
   <si>
     <t>['define_ramp_limit_constraints', 'define_nodal_balance_constraints', 'define_operational_constraints_for_committables']</t>
@@ -669,352 +669,6 @@
     <t>8c3081a7c5eb28fb0655901a679118904d8225a3</t>
   </si>
   <si>
-    <t>pypsa 0.22 doesn't work with matplotlib 3.4.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (ImportError: cannot import name 'colormaps' from 'matplotlib'), but it does work with 3.6.3 - add to dependencies environment.yaml</t>
-  </si>
-  <si>
-    <t>https://github.com/PyPSA/PyPSA/issues/558</t>
-  </si>
-  <si>
-    <t>['pypsa/plot.py']</t>
-  </si>
-  <si>
-    <t>['plot']</t>
-  </si>
-  <si>
-    <t>[308]</t>
-  </si>
-  <si>
-    <t>https://github.com/pypsa/pypsa/compare/129a59769b8578700af276d21bec047236009222...36b89c1da79452671209adcafb9f571f791596e7</t>
-  </si>
-  <si>
-    <t>129a59769b8578700af276d21bec047236009222</t>
-  </si>
-  <si>
-    <t>36b89c1da79452671209adcafb9f571f791596e7</t>
-  </si>
-  <si>
-    <t>SCLOPF returns TypeError with pyomo=False unless run with pyomo=True first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">## Checklist_x000D_
-_x000D_
-- [x] I am using the current [`master`](https://github.com/pypsa/pypsa/tree/master) branch or the latest [release](https://github.com/pypsa/pypsa/releases). Please indicate:_x000D_
-_x000D_
-## Describe the Bug_x000D_
-_x000D_
-Running `sclopf` with `pyomo=False` returns a concatenation-related `TypeError`. However, running `sclopf` with `pyomo=True` on the same network and then running with `pyomo=False` again works. This explains why the unit test (which runs in a loop with True first then False) does not fail. First observed this on my own case then reproduced using the unit test case._x000D_
-_x000D_
-## (MWE and) Error Message_x000D_
-MWE (repurposed from `test_sclopf_scigrid.py`):_x000D_
-_x000D_
-```python_x000D_
-In [1]: import pypsa_x000D_
-_x000D_
-In [2]: n = pypsa.Network("../../PyPSA/examples/scigrid-de/scigrid-with-load-gen-trafos/")_x000D_
-WARNING:pypsa.io:_x000D_
-Importing PyPSA from older version of PyPSA than current version._x000D_
-Please read the release notes at https://pypsa.readthedocs.io/en/latest/release_notes.html_x000D_
-carefully to prepare your network for import._x000D_
-Currently used PyPSA version [0, 20, 0], imported network file PyPSA version [0, 10, 0]._x000D_
-_x000D_
-INFO:pypsa.components:Applying weightings to all columns of `snapshot_weightings`_x000D_
-INFO:pypsa.io:Imported network nan has buses, generators, lines, loads, storage_units, transformers_x000D_
-_x000D_
-In [3]: for line_name in ["316", "527", "602"]:_x000D_
-   ...:     n.lines.loc[line_name, "s_nom"] = 1200_x000D_
-   ...: branch_outages = n.lines.index[:2]_x000D_
-_x000D_
-In [4]: n.sclopf(_x000D_
-   ...:     n.snapshots[0],_x000D_
-   ...:     branch_outages=branch_outages,_x000D_
-   ...:     pyomo=False,  # running with pyomo=False first_x000D_
-   ...:     solver_name="cbc",_x000D_
-   ...: )_x000D_
-INFO:pypsa.linopf:Prepare linear problem_x000D_
----------------------------------------------------------------------------_x000D_
-TypeError                                 Traceback (most recent call last)_x000D_
-Input In [4], in &lt;cell line: 1&gt;()_x000D_
-----&gt; 1 n.sclopf(_x000D_
-      2     n.snapshots[0],_x000D_
-      3     branch_outages=branch_outages,_x000D_
-      4     pyomo=False,_x000D_
-      5     solver_name="cbc",_x000D_
-      6 )_x000D_
-_x000D_
-File ~/PyPSA/pypsa/contingency.py:464, in network_sclopf(network, snapshots, branch_outages, solver_name, pyomo, skip_pre, extra_functionality, solver_options, keep_files, formulation, ptdf_tolerance)_x000D_
-    460     pyomo_kwargs["ptdf_tolerance"] = ptdf_tolerance_x000D_
-    462 # need to skip preparation otherwise it recalculates the sub-networks_x000D_
---&gt; 464 network.lopf(_x000D_
-    465     snapshots=snapshots,_x000D_
-    466     solver_name=solver_name,_x000D_
-    467     pyomo=pyomo,_x000D_
-    468     skip_pre=True,_x000D_
-    469     extra_functionality=_extra_functionality,_x000D_
-    470     solver_options=solver_options,_x000D_
-    471     keep_files=keep_files,_x000D_
-    472     formulation=formulation,_x000D_
-    473     **pyomo_kwargs,_x000D_
-    474 )_x000D_
-_x000D_
-File ~/PyPSA/pypsa/components.py:752, in Network.lopf(self, snapshots, pyomo, solver_name, solver_options, solver_logfile, formulation, keep_files, extra_functionality, multi_investment_periods, **kwargs)_x000D_
-    750     return network_lopf(self, **args)_x000D_
-    751 else:_x000D_
---&gt; 752     return network_lopf_lowmem(self, **args)_x000D_
-_x000D_
-File ~/PyPSA/pypsa/linopf.py:1450, in network_lopf(n, snapshots, solver_name, solver_logfile, extra_functionality, multi_investment_periods, skip_objective, skip_pre, extra_postprocessing, formulation, keep_references, keep_files, keep_shadowprices, solver_options, warmstart, store_basis, solver_dir)_x000D_
-   1447     n.determine_network_topology()_x000D_
-   1449 logger.info("Prepare linear problem")_x000D_
--&gt; 1450 fdp, problem_fn = prepare_lopf(_x000D_
-   1451     n, snapshots, keep_files, skip_objective, extra_functionality, solver_dir_x000D_
-   1452 )_x000D_
-   1453 fds, solution_fn = mkstemp(prefix="pypsa-solve", suffix=".sol", dir=solver_dir)_x000D_
-   1455 if warmstart == True:_x000D_
-_x000D_
-File ~/PyPSA/pypsa/linopf.py:1107, in prepare_lopf(n, snapshots, keep_files, skip_objective, extra_functionality, solver_dir)_x000D_
-   1105 define_storage_unit_constraints(n, snapshots)_x000D_
-   1106 define_store_constraints(n, snapshots)_x000D_
--&gt; 1107 define_kirchhoff_constraints(n, snapshots)_x000D_
-   1108 define_nodal_balance_constraints(n, snapshots)_x000D_
-   1109 define_global_constraints(n, snapshots)_x000D_
-_x000D_
-File ~/PyPSA/pypsa/linopf.py:508, in define_kirchhoff_constraints(n, sns)_x000D_
-    505     snapshots = sns if period == None else sns[sns.get_loc(period)]_x000D_
-    506     cycle_sum.set_index(snapshots, inplace=True)_x000D_
---&gt; 508     con = write_constraint(n, cycle_sum, "=", 0)_x000D_
-    509     subconstraints.append(con)_x000D_
-    510 if len(subconstraints) == 0:_x000D_
-_x000D_
-File ~/PyPSA/pypsa/linopt.py:270, in write_constraint(n, lhs, sense, rhs, axes, mask)_x000D_
-    268     sense = "=" if sense == "==" else sense_x000D_
-    269 lhs, sense, rhs = _str_array(lhs), _str_array(sense), _str_array(rhs)_x000D_
---&gt; 270 exprs = "c" + _str_array(cons, True) + ":\\n" + lhs + sense + " " + rhs + "\\n\\n"_x000D_
-    271 if mask is not None:_x000D_
-    272     exprs = np.where(mask, exprs, "")_x000D_
-_x000D_
-TypeError: can only concatenate str (not "int") to str_x000D_
-_x000D_
-In [5]: n.sclopf(_x000D_
-   ...:     n.snapshots[0],_x000D_
-   ...:     branch_outages=branch_outages,_x000D_
-   ...:     pyomo=True,  # running with pyomo=True works_x000D_
-   ...:     solver_name="cbc",_x000D_
-   ...: )_x000D_
-WARNING:pypsa.components:Solving optimisation problem with pyomo.In PyPSA version 0.21 the default will change to ``n.lopf(pyomo=False)``.Explicitly set ``n.lopf(pyomo=True)`` to retain current behaviour._x000D_
-INFO:pypsa.opf:Building pyomo model using `kirchhoff` formulation_x000D_
-WARNING:pypsa.contingency:No type given for 1, assuming it is a line_x000D_
-WARNING:pypsa.contingency:No type given for 2, assuming it is a line_x000D_
-INFO:pypsa.opf:Solving model using cbc_x000D_
-# ==========================================================_x000D_
-# = Solver Results                                         =_x000D_
-# ==========================================================_x000D_
-# ----------------------------------------------------------_x000D_
-#   Problem Information_x000D_
-# ----------------------------------------------------------_x000D_
-Problem: _x000D_
-- Name: unknown_x000D_
-  Lower bound: 339758.4578_x000D_
-  Upper bound: 339758.4578_x000D_
-  Number of objectives: 1_x000D_
-  Number of constraints: 6714_x000D_
-  Number of variables: 2486_x000D_
-  Number of nonzeros: 438_x000D_
-  Sense: minimize_x000D_
-# ----------------------------------------------------------_x000D_
-#   Solver Information_x000D_
-# ----------------------------------------------------------_x000D_
-Solver: _x000D_
-- Status: ok_x000D_
-  User time: -1.0_x000D_
-  System time: 0.13_x000D_
-  Wallclock time: 0.14_x000D_
-  Termination condition: optimal_x000D_
-  Termination message: Model was solved to optimality (subject to tolerances), and an optimal solution is available._x000D_
-  Statistics: _x000D_
-    Branch and bound: _x000D_
-      Number of bounded subproblems: None_x000D_
-      Number of created subproblems: None_x000D_
-    Black box: _x000D_
-      Number of iterations: 760_x000D_
-  Error rc: 0_x000D_
-  Time: 0.15059161186218262_x000D_
-# ----------------------------------------------------------_x000D_
-#   Solution Information_x000D_
-# ----------------------------------------------------------_x000D_
-Solution: _x000D_
-- number of solutions: 0_x000D_
-  number of solutions displayed: 0_x000D_
-INFO:pypsa.opf:Optimization successful_x000D_
-_x000D_
-In [6]: n.sclopf(_x000D_
-   ...:     n.snapshots[0],_x000D_
-   ...:     branch_outages=branch_outages,_x000D_
-   ...:     pyomo=False,  # after successfully running with pyomo=True, running again with False (same as In[4]) works fine._x000D_
-   ...:     solver_name="cbc",_x000D_
-   ...: )_x000D_
-INFO:pypsa.linopf:Prepare linear problem_x000D_
-INFO:pypsa.linopf:Total preparation time: 4.23s_x000D_
-INFO:pypsa.linopf:Solve linear problem using Cbc solver_x000D_
-INFO:pypsa.linopf:Optimization successful. Objective value: 3.40e+05_x000D_
-```_x000D_
-</t>
-  </si>
-  <si>
-    <t>https://github.com/PyPSA/PyPSA/issues/436</t>
-  </si>
-  <si>
-    <t>['pypsa/contingency.py', 'test/conftest.py', 'test/test_sclopf_scigrid.py']</t>
-  </si>
-  <si>
-    <t>['test_sclopf_pyomo', 'network_sclopf', 'test_sclopf', 'scipy_network']</t>
-  </si>
-  <si>
-    <t>[436, 18, 4, 11, 12, 22, 23, 24, 25, 26, 27, 29, 30, 31, 33, 35, 37, 39, 40, 41, 43, 45]</t>
-  </si>
-  <si>
-    <t>https://github.com/pypsa/pypsa/compare/9eeffb18ebeeae0448d36579c52738496ee7388b...632d62528c6118058c13d7e68b414d18bb6708c6</t>
-  </si>
-  <si>
-    <t>9eeffb18ebeeae0448d36579c52738496ee7388b</t>
-  </si>
-  <si>
-    <t>632d62528c6118058c13d7e68b414d18bb6708c6</t>
-  </si>
-  <si>
-    <t>"p_nom": pd.Series.min aggregation default reduces capacity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;!-- Please do not post usage questions here. Ask them on the PyPSA mailing list: https://groups.google.com/forum/#!forum/pypsa --&gt;_x000D_
-_x000D_
-## Checklist_x000D_
-_x000D_
-- [x] I am using the current [`master`](https://github.com/pypsa/pypsa/tree/master) branch or the latest [release](https://github.com/pypsa/pypsa/releases). Please indicate:_x000D_
-_x000D_
-## Describe the Bug_x000D_
-_x000D_
-The default aggregation strategies are set in `networkclustering.py`_x000D_
-https://github.com/PyPSA/PyPSA/blob/daead70515d877fd273cc294ffa1734c218f2831/pypsa/networkclustering.py#L86-L98_x000D_
-_x000D_
-We observed [here](https://github.com/pypsa-meets-africa/pypsa-africa/issues/431) the following behaviour using the PyPSA default aggregation strategies:_x000D_
-_x000D_
-PyPSA-Africa: Powerplants in Nigeria **8GW**, after applying the aggregation strategy `p_nom: min` **5GW**, after fix `p_nom: sum` **8GW** _x000D_
-PyPSA-Africa: Powerplants in Africa **121GW**, after applying the aggregation strategy `p_nom: min` **21GW**_x000D_
-PyPSA-Eur: Powerplant in Europe **476GW**, after applying the aggregation strategy `p_nom: min` **339GW**, after fix `p_nom: sum` **476GW**_x000D_
-_x000D_
-I think the `"p_nom": pd.Series.sum` is an untended default setting introducing major capacity reductions. I would even argue that using `min` can be considered as bug. When clustering the powerplant capacities of e.g. 5 nodes, I want to have all 5 powerplants represented as `sum` in the resulting clustered node.  Therefore, I think we should make `"p_nom": pd.Series.sum` the default. </t>
-  </si>
-  <si>
-    <t>https://github.com/PyPSA/PyPSA/issues/429</t>
-  </si>
-  <si>
-    <t>['pypsa/networkclustering.py']</t>
-  </si>
-  <si>
-    <t>['aggregategenerators']</t>
-  </si>
-  <si>
-    <t>[89]</t>
-  </si>
-  <si>
-    <t>https://github.com/pypsa/pypsa/compare/daead70515d877fd273cc294ffa1734c218f2831...73f92fa382468eb7ee0bea852eed6deb2112db23</t>
-  </si>
-  <si>
-    <t>daead70515d877fd273cc294ffa1734c218f2831</t>
-  </si>
-  <si>
-    <t>73f92fa382468eb7ee0bea852eed6deb2112db23</t>
-  </si>
-  <si>
-    <t>Minor issue: network.objective not updated after failed lopf</t>
-  </si>
-  <si>
-    <t>A failed run with solvers in lopf (possibly other variants too) does not cause an Exception, which is good I think. Unless there's min_up_time and so forth some failed days don't hurt and can investigate after._x000D_
-Minor issue is that network.objective is not updated it seems, but keeps the last value (of the day before). A simple check against network.objective to see whether the run succeeded fails, as does the sum of the objective. _x000D_
-Both pyomo True and False are affected, also tested with Gurobi._x000D_
-_x000D_
-```_x000D_
-import pypsa_x000D_
-import numpy as np_x000D_
-_x000D_
-n = pypsa.Network()_x000D_
-n.add('Bus', 'bus')_x000D_
-n.add('Generator', bus='bus', name='generator', p_nom=100, control='slack', marginal_cost=1)_x000D_
-n.add('Load', 'load', bus='bus')_x000D_
-_x000D_
-n.set_snapshots(np.arange(3))_x000D_
-n.loads_t['p_set'].loc[:, 'load'] = np.array([80,120,90])_x000D_
-_x000D_
-objective = []_x000D_
-for i in [0,1,2]:_x000D_
-    n.lopf(snapshots=i, solver_name='cbc', pyomo=True)_x000D_
-    objective.append(n.objective)_x000D_
-_x000D_
-print(objective)_x000D_
-```_x000D_
-_x000D_
-.. will yield [80,80,90] instead of [80, nan, 90].</t>
-  </si>
-  <si>
-    <t>https://github.com/PyPSA/PyPSA/issues/397</t>
-  </si>
-  <si>
-    <t>['pypsa/opf.py', 'pypsa/linopf.py']</t>
-  </si>
-  <si>
-    <t>['network_lopf', 'network_lopf_solve']</t>
-  </si>
-  <si>
-    <t>[1492, 2343]</t>
-  </si>
-  <si>
-    <t>https://github.com/pypsa/pypsa/compare/7572e2252266e62070d48789f9dd2e336e5bb309...fa7086c8a27856ce78540ff07af3c03bc7c909e5</t>
-  </si>
-  <si>
-    <t>7572e2252266e62070d48789f9dd2e336e5bb309</t>
-  </si>
-  <si>
-    <t>fa7086c8a27856ce78540ff07af3c03bc7c909e5</t>
-  </si>
-  <si>
-    <t>pypsa does not work with Pyomo 6.4.3</t>
-  </si>
-  <si>
-    <t>&lt;!-- Please do not post usage questions here. Ask them on the PyPSA mailing list: https://groups.google.com/forum/#!forum/pypsa --&gt;_x000D_
-_x000D_
-## Checklist_x000D_
-_x000D_
-- [ ] I am using the current [`master`](https://github.com/pypsa/pypsa/tree/master) branch or the latest [release](https://github.com/pypsa/pypsa/releases). Please indicate: 0.21.1_x000D_
-_x000D_
-## Describe the Bug_x000D_
-_x000D_
-`from pyomo.core.expr.logical_expr import inequality` in `opt.py` produces an error with pyomo 6.4.3_x000D_
-_x000D_
-`ImportError: cannot import name 'inequality' from 'pyomo.core.expr.logical_expr'` as it was moved to `pyomo.core.expr.relational_expr`_x000D_
-_x000D_
-To fix this, the import should be `from pyomo.environ import inequality` as this is meant as the public import without assuming the internal package structure of pyomo which might change again in the future._x000D_
-https://github.com/Pyomo/pyomo/blob/main/pyomo/core/tests/unit/test_relational_expr.py#L24</t>
-  </si>
-  <si>
-    <t>https://github.com/PyPSA/PyPSA/issues/511</t>
-  </si>
-  <si>
-    <t>['pypsa/opt.py']</t>
-  </si>
-  <si>
-    <t>[31]</t>
-  </si>
-  <si>
-    <t>https://github.com/pypsa/pypsa/compare/776828f08f8de89b0eca43b8f097620288722570...52f994a6a8c4dc6c1f58e506639008560c92ad67</t>
-  </si>
-  <si>
-    <t>776828f08f8de89b0eca43b8f097620288722570</t>
-  </si>
-  <si>
-    <t>52f994a6a8c4dc6c1f58e506639008560c92ad67</t>
-  </si>
-  <si>
     <t>spritelink/nipap</t>
   </si>
   <si>
@@ -1031,13 +685,13 @@
     <t>https://github.com/SpriteLink/NIPAP/issues/954</t>
   </si>
   <si>
-    <t>['nipap/nipap/smart_parsing.py', 'tests/nipaptest.py']</t>
-  </si>
-  <si>
-    <t>['TestSmartParser', 'PrefixSmartParser', 'SmartParser']</t>
-  </si>
-  <si>
-    <t>['test_prefix11', 'test_prefix10', 'test_prefix8', 'test_prefix7', 'test_vrf1', 'test_prefix12', 'test_prefix9']</t>
+    <t>['tests/nipaptest.py', 'nipap/nipap/smart_parsing.py']</t>
+  </si>
+  <si>
+    <t>['SmartParser', 'PrefixSmartParser', 'TestSmartParser']</t>
+  </si>
+  <si>
+    <t>['test_prefix7', 'test_prefix11', 'test_prefix9', 'test_vrf1', 'test_prefix12', 'test_prefix8', 'test_prefix10']</t>
   </si>
   <si>
     <t>[105, 106, 107, 108, 125, 193, 450, 451, 452, 453, 454, 455, 456, 457, 458, 459, 460, 461, 462, 463, 464, 465, 466, 467, 468, 469, 470, 471, 472, 473, 474, 475, 476, 477, 478, 479, 480, 481, 482, 483, 485, 486, 2033, 2034, 2035, 2036, 2037, 2038, 2039, 2040, 2041, 2042, 2043, 2044, 2045, 2046, 2047, 2048, 2049, 2050, 2051, 2052, 2053, 2054, 2055, 2056, 2057, 2058, 2059, 2060, 2061, 2062, 2063, 2064, 2065, 2066, 2067, 2068, 2069, 2070, 2071, 2072, 2073, 2074, 2075, 2076, 2077, 2078, 2079, 2080, 2081, 2082, 2083, 2084, 2085, 2086, 2087, 2088, 2089, 2090, 2091, 2092, 2093, 2094, 2095, 2096, 2097, 2098, 2099, 2100, 2101, 2102, 2103, 2104, 2105, 2106, 2107, 2108, 2109, 2110, 2111, 2112, 2113, 2114, 2115, 2116, 2117, 2118, 2119, 2120, 2121, 2122, 2123, 2124, 2125, 2126, 2127, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2140, 2141, 2142, 2143, 2144, 2145, 2146, 2147, 2148, 2149, 2150, 2151, 2152, 2153, 2154, 2155, 2156]</t>
@@ -1221,175 +875,6 @@
     <t>97b34a878197e89ad2eff5f37dc57c820a1bbe54</t>
   </si>
   <si>
-    <t>Broken prefix list page web UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check out nipap-demo.spritelink.net - I'm just getting a big ugly error message: "undefined".
-I ran nipapd with -d -f and it appears to work OK.
-Could this be that the web-UI expects the interpretation result to look differently? 
-</t>
-  </si>
-  <si>
-    <t>https://github.com/SpriteLink/NIPAP/issues/1004</t>
-  </si>
-  <si>
-    <t>['nipap-www/nipapwww/controllers/xhr.py']</t>
-  </si>
-  <si>
-    <t>['XhrController']</t>
-  </si>
-  <si>
-    <t>[112, 113, 114, 115, 116, 117, 242, 243, 244, 245, 246, 247, 511, 512, 513, 514, 515, 516]</t>
-  </si>
-  <si>
-    <t>https://github.com/spritelink/nipap/compare/df9ac80c238d3d052b661237a993df8b27d3eb12...59404e82d5756e7b4a6261cec0eaf7ead9f5e30c</t>
-  </si>
-  <si>
-    <t>df9ac80c238d3d052b661237a993df8b27d3eb12</t>
-  </si>
-  <si>
-    <t>59404e82d5756e7b4a6261cec0eaf7ead9f5e30c</t>
-  </si>
-  <si>
-    <t>Response on smart parser error incorrect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The response sent when the smart parser encounters an error does not follow the same format as for a successful query, which leads to parser error messages not being displayed:
-```
-$ ./nipap --show-interpretation a l 'foo "'
-Searching for prefixes in any VRF...
-Query interpretation:
-No addresses matching 'foo "' found.
-```
-Here I'd expect the error message to be displayed.
-</t>
-  </si>
-  <si>
-    <t>https://github.com/SpriteLink/NIPAP/issues/982</t>
-  </si>
-  <si>
-    <t>['nipap/nipap/backend.py', 'tests/nipaptest.py']</t>
-  </si>
-  <si>
-    <t>['Nipap', 'TestPrefixLastModified', 'TestAddressListing']</t>
-  </si>
-  <si>
-    <t>['test_invalid_search_string']</t>
-  </si>
-  <si>
-    <t>[1667, 1668, 1669, 1670, 1671, 1673, 1674, 1675, 1677, 2289, 2290, 2291, 2292, 2293, 2294, 2295, 2296, 2297, 2298, 2299, 2300, 2301, 2302, 3637, 3638, 3639, 3640, 3641, 3644, 3645, 3647, 4113, 4114, 4115, 4116, 4117, 4120, 4121, 4123, 1543, 1544, 1545, 1546, 1547, 1548, 1549, 1550, 1551, 1552, 1553, 1554, 1555, 1556, 1557, 1558, 1559, 1560, 1561, 1562, 1563, 1564, 1565, 1566, 1567, 1568, 1569, 1570, 1571, 1572, 1573, 1574, 1575, 1576]</t>
-  </si>
-  <si>
-    <t>https://github.com/spritelink/nipap/compare/b1e45276931974c3aa6fdbe3e0d9774c7e2c1c71...0e0d4c2a3a5c6f9b332fdc1803338ba54a37e105</t>
-  </si>
-  <si>
-    <t>b1e45276931974c3aa6fdbe3e0d9774c7e2c1c71</t>
-  </si>
-  <si>
-    <t>0e0d4c2a3a5c6f9b332fdc1803338ba54a37e105</t>
-  </si>
-  <si>
-    <t>Prefix smart parser lacks the prefix_length attribute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The prefix smart parser lacks the prefix_length attribute.
-Perhaps we could use the list of attributes in backend.py to populate the attribute lists in the smart parser classes?
-</t>
-  </si>
-  <si>
-    <t>https://github.com/SpriteLink/NIPAP/issues/973</t>
-  </si>
-  <si>
-    <t>['nipap/nipap/smart_parsing.py']</t>
-  </si>
-  <si>
-    <t>['PrefixSmartParser']</t>
-  </si>
-  <si>
-    <t>[409]</t>
-  </si>
-  <si>
-    <t>https://github.com/spritelink/nipap/compare/a3db7424d0dfb07168dc341a0148be6e25791392...58225ad9ab15e294de8a6807e1a2a241f5512dc8</t>
-  </si>
-  <si>
-    <t>a3db7424d0dfb07168dc341a0148be6e25791392</t>
-  </si>
-  <si>
-    <t>58225ad9ab15e294de8a6807e1a2a241f5512dc8</t>
-  </si>
-  <si>
-    <t>Not specifying status results in error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creating a prefix with pynipap results in an error being thrown from the back end if 'status' is not explicitly specified:
-```
-In [4]: p = pynipap.Prefix()
-In [5]: p.prefix = '1.3.3.0/24'
-In [6]: p.type = 'reservation'
-In [7]: p.description = 'Test'
-In [8]: p.save()
----------------------------------------------------------------------------
-NipapError                                Traceback (most recent call last)
-&lt;ipython-input-8-395e325a0c83&gt; in &lt;module&gt;()
-----&gt; 1 p.save()
-/home/lukagarb/dev/venv/lib/python2.7/site-packages/pynipap.pyc in save(self, args)
-   1029                     })
-   1030             except xmlrpclib.Fault as xml_fault:
--&gt; 1031                 raise _fault_to_exception(xml_fault)
-   1032
-   1033         # Old object, edit
-NipapError: null value in column "status" violates not-null constraint
-DETAIL:  Failing row contains (5625, 0, 1.3.3.0/24, 1.3.3.0/24, Test, null, null, null, reservation, 0, null, null, null, null, asdf, null, null, 0, null, {}, {}, 2014-11-07 11:04:21.945863+01, 2014-11-07 11:04:21.945863+01, 256, 0, 256, , null, infinity).
-In [9]:
-```
-The expected behavior would IMHO be to have the prefix added with a sane default, such as 'assigned'. I'd say that the backend handles this correctly by throwing an error; pynipap should not pass the 'status' attribute to the add_prefix function when it's not been set.
-</t>
-  </si>
-  <si>
-    <t>https://github.com/SpriteLink/NIPAP/issues/668</t>
-  </si>
-  <si>
-    <t>['pynipap/pynipap.py']</t>
-  </si>
-  <si>
-    <t>['Prefix']</t>
-  </si>
-  <si>
-    <t>[987, 988, 989, 990]</t>
-  </si>
-  <si>
-    <t>https://github.com/spritelink/nipap/compare/2f10dedaac0bd5602635bc30ac88c62a34acd5fe...af2e61806175d77a661a7a92a2dddff43880e9d3</t>
-  </si>
-  <si>
-    <t>2f10dedaac0bd5602635bc30ac88c62a34acd5fe</t>
-  </si>
-  <si>
-    <t>af2e61806175d77a661a7a92a2dddff43880e9d3</t>
-  </si>
-  <si>
-    <t>pynipap.NipapError: &lt;type 'exceptions.UnboundLocalError'&gt;:local variable 'q' referenced before assignment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I believe I've found a bug - I'm not entirely sure how I'm triggering it, and what I'm doing is likely wrong, but I don't think it should be returning this response
-I've tracked down the erroring code to https://github.com/SpriteLink/NIPAP/blob/master/nipap/nipap/backend.py#L991
-</t>
-  </si>
-  <si>
-    <t>https://github.com/SpriteLink/NIPAP/issues/843</t>
-  </si>
-  <si>
-    <t>[990, 991, 992, 993, 994, 995, 996, 997, 998, 999, 1000, 1001, 1002]</t>
-  </si>
-  <si>
-    <t>https://github.com/spritelink/nipap/compare/099ae49d2d9663174f02ca8be88f6676dc0b37cf...411a8d234ad0c8fe5e9db5e61782c7e5f7681c91</t>
-  </si>
-  <si>
-    <t>099ae49d2d9663174f02ca8be88f6676dc0b37cf</t>
-  </si>
-  <si>
-    <t>411a8d234ad0c8fe5e9db5e61782c7e5f7681c91</t>
-  </si>
-  <si>
     <t>nf-core/tools</t>
   </si>
   <si>
@@ -1499,7 +984,7 @@
     <t>https://github.com/nf-core/tools/issues/2148</t>
   </si>
   <si>
-    <t>['nf_core/schema.py', 'nf_core/__main__.py']</t>
+    <t>['nf_core/__main__.py', 'nf_core/schema.py']</t>
   </si>
   <si>
     <t>['PipelineSchema']</t>
@@ -1580,10 +1065,10 @@
     <t>https://github.com/nf-core/tools/issues/2119</t>
   </si>
   <si>
-    <t>['nf_core/subworkflows/create.py', 'nf_core/modules/create.py', 'nf_core/components/components_create.py']</t>
-  </si>
-  <si>
-    <t>['ModuleCreate', 'SubworkflowCreate']</t>
+    <t>['nf_core/modules/create.py', 'nf_core/components/components_create.py', 'nf_core/subworkflows/create.py']</t>
+  </si>
+  <si>
+    <t>['SubworkflowCreate', 'ModuleCreate']</t>
   </si>
   <si>
     <t>['get_username']</t>
@@ -1667,196 +1152,6 @@
     <t>6451429a5f6ee314b749167d7b03894d654fd8b1</t>
   </si>
   <si>
-    <t>modules create-test-yml broken for alternative remotes</t>
-  </si>
-  <si>
-    <t>This command is broken when running in a repo which is not the default `nf-core/modules` (or possibly a direct mirror of)._x000D_
-_x000D_
-The underlying class does not currently take `--git-remote` in it's init and when selecting the module it uses `ModulesRepo()` which will always use the default NF-Core remote.   _x000D_
-_x000D_
-tools 2.7dev0</t>
-  </si>
-  <si>
-    <t>https://github.com/nf-core/tools/issues/2083</t>
-  </si>
-  <si>
-    <t>['nf_core/modules/test_yml_builder.py', 'nf_core/subworkflows/test_yml_builder.py', 'tests/modules/create_test_yml.py', 'nf_core/__main__.py']</t>
-  </si>
-  <si>
-    <t>['SubworkflowTestYmlBuilder', 'ModulesTestYmlBuilder']</t>
-  </si>
-  <si>
-    <t>['run', 'create_test_yml', 'test_modules_test_file_dict', 'test_modules_custom_yml_dumper']</t>
-  </si>
-  <si>
-    <t>[736, 737, 984, 985, 43, 44, 46, 48, 49, 84, 103, 179, 180, 45, 46, 51, 52, 62, 85, 2, 8, 24]</t>
-  </si>
-  <si>
-    <t>https://github.com/nf-core/tools/compare/f0b6c48b3a3b729669e34cf7150da449e381f8f8...69cfe0444dd2f24c30978d750bb45e958f5897c7</t>
-  </si>
-  <si>
-    <t>f0b6c48b3a3b729669e34cf7150da449e381f8f8</t>
-  </si>
-  <si>
-    <t>69cfe0444dd2f24c30978d750bb45e958f5897c7</t>
-  </si>
-  <si>
-    <t>installed_by field is not properly updated when updating a subworkflow</t>
-  </si>
-  <si>
-    <t>### Description of the bug
-I installed a subworkflow (`vcf_annotate_ensemblvep`) on sarek, I had an on-going PR for it._x000D_
-The subworkflow had some modifications (`TABIX_BGZIPTABIX` was removed and `TABIX_TABIX` was added) so I updated it, and it was well updated, without issues._x000D_
-But when inspecting the `modules.json`, I noticed that `TABIX_BGZIPTABIX` was still listed as installed by `vcf_annotate_ensemblvep`
-### Command used and terminal output
-_No response_
-### System information
-_No response_</t>
-  </si>
-  <si>
-    <t>https://github.com/nf-core/tools/issues/2065</t>
-  </si>
-  <si>
-    <t>['nf_core/modules/modules_json.py', 'nf_core/components/update.py', 'tests/test_subworkflows.py', 'tests/subworkflows/update.py']</t>
-  </si>
-  <si>
-    <t>['ComponentUpdate', 'TestSubworkflows', 'ModulesJson']</t>
-  </si>
-  <si>
-    <t>['cmp_component', 'test_update_all_subworkflows_from_module', 'test_update_change_of_included_modules', '_change_component_type', 'manage_changes_in_linked_components']</t>
-  </si>
-  <si>
-    <t>[12, 13, 14, 15, 16, 17, 262, 287, 308, 312, 313, 314, 315, 316, 317, 886, 887, 888, 889, 890, 891, 892, 893, 894, 895, 896, 897, 898, 899, 900, 901, 902, 903, 904, 905, 906, 907, 908, 909, 910, 911, 912, 913, 659, 299, 300, 301, 302, 303, 304, 305, 306, 307, 308, 309, 310, 311, 312, 313, 314, 315, 316, 317, 318, 319, 320, 321, 322, 323, 324, 325, 70, 71, 72, 73, 74, 75, 135]</t>
-  </si>
-  <si>
-    <t>https://github.com/nf-core/tools/compare/77ec31e874d03bcf3bf53e5bd66f9ae34c0f6857...ae70b7861dc6456e4b51e42036e6653cfd943bc8</t>
-  </si>
-  <si>
-    <t>77ec31e874d03bcf3bf53e5bd66f9ae34c0f6857</t>
-  </si>
-  <si>
-    <t>ae70b7861dc6456e4b51e42036e6653cfd943bc8</t>
-  </si>
-  <si>
-    <t>Restore remote options to &lt;modules/subworkflows&gt; remove command</t>
-  </si>
-  <si>
-    <t>### Description of the bug
-Recent updates to &lt;modules/subworkflows&gt; remove got rid of the remote options for the command. _x000D_
-This has caused it to be impossible to remove non-nf-core components via the command. 
-### Command used and terminal output
-```console
-nf-core modules --git-remote &lt;my-git-url&gt; remove_x000D_
-_x000D_
-Pulling from 'nf-core/modules' (https://github.com/nf-core/modules.git)_x000D_
-CRITICAL Nothing installed from nf-core/modules in pipeline
-```
-### System information
-_No response_</t>
-  </si>
-  <si>
-    <t>https://github.com/nf-core/tools/issues/2041</t>
-  </si>
-  <si>
-    <t>['tests/test_modules.py', 'nf_core/modules/remove.py', 'nf_core/subworkflows/remove.py', 'nf_core/modules/modules_json.py', 'tests/modules/remove.py', 'nf_core/__main__.py', 'nf_core/components/remove.py']</t>
-  </si>
-  <si>
-    <t>['ComponentRemove', 'ModulesJson', 'ModuleRemove', 'TestModules', 'SubworkflowRemove']</t>
-  </si>
-  <si>
-    <t>['remove', '__init__', 'test_modules_remove_trimgalore_uninstalled', 'test_modules_remove_multiqc_from_gitlab']</t>
-  </si>
-  <si>
-    <t>[639, 640, 641, 642, 643, 644, 1202, 1203, 1204, 1205, 1206, 1207, 19, 20, 688, 689, 9, 10, 9, 10, 17, 18, 19, 20, 21, 22, 98, 99, 100, 101, 102, 202]</t>
-  </si>
-  <si>
-    <t>https://github.com/nf-core/tools/compare/bbb5415f1fb99443c96259698ead7034242cc504...aefa3d5e5f53311dfffa33aa3cd2bba5391a1416</t>
-  </si>
-  <si>
-    <t>bbb5415f1fb99443c96259698ead7034242cc504</t>
-  </si>
-  <si>
-    <t>aefa3d5e5f53311dfffa33aa3cd2bba5391a1416</t>
-  </si>
-  <si>
-    <t>Template for test yaml is incorrect when using "contains"</t>
-  </si>
-  <si>
-    <t>### Description of the bug
-"contains" in `test_yml_builder.py` in both `subworklows` and `modules` is currently outputting a string in the yml but it needs to be an array of strings._x000D_
-_x000D_
-See https://github.com/nf-core/modules/pull/2204_x000D_
-_x000D_
-### Command used and terminal output
-_No response_
-### System information
-Tools version 2.7</t>
-  </si>
-  <si>
-    <t>https://github.com/nf-core/tools/issues/1922</t>
-  </si>
-  <si>
-    <t>['nf_core/modules/test_yml_builder.py', 'nf_core/subworkflows/test_yml_builder.py', 'nf_core/modules/modules_repo.py']</t>
-  </si>
-  <si>
-    <t>['SubworkflowTestYmlBuilder', 'ModulesRepo', 'ModulesTestYmlBuilder']</t>
-  </si>
-  <si>
-    <t>[384, 385, 386, 387, 290, 291, 292, 308, 309, 310]</t>
-  </si>
-  <si>
-    <t>https://github.com/nf-core/tools/compare/be8978bad527172c4a32b4888e8abfe5fe5954d8...940a7bd5fd7b56ea45db40c09332181720683cb5</t>
-  </si>
-  <si>
-    <t>be8978bad527172c4a32b4888e8abfe5fe5954d8</t>
-  </si>
-  <si>
-    <t>940a7bd5fd7b56ea45db40c09332181720683cb5</t>
-  </si>
-  <si>
-    <t>Prettier fails linting for default modules.json</t>
-  </si>
-  <si>
-    <t>### Description of the bug_x000D_
-_x000D_
-The `modules.json` was created using `nf-core modules` and `nf-core subworkflows` commands using the latest code on `dev`. However, linting fails with Prettier which wants to put the `installed_by` section on a single line. We should either ignore this file or fix the default output from tools._x000D_
-_x000D_
-```diff_x000D_
-                    "ataqv/ataqv": {_x000D_
-                         "branch": "master",_x000D_
-                         "git_sha": "56421e1a812bc2f9e77dbe9f297e9d9c580cb8a5",_x000D_
--                        "installed_by": [_x000D_
--                            "modules"_x000D_
--                        ]_x000D_
-+                        "installed_by": ["modules"]_x000D_
-                     },_x000D_
-```</t>
-  </si>
-  <si>
-    <t>https://github.com/nf-core/tools/issues/2047</t>
-  </si>
-  <si>
-    <t>['tests/test_lint_utils.py', 'nf_core/modules/modules_json.py', 'nf_core/lint_utils.py']</t>
-  </si>
-  <si>
-    <t>['ModulesJson']</t>
-  </si>
-  <si>
-    <t>['git_dir_with_json_syntax_error', 'get_component_names_from_repo', 'resolve_missing_installation', 'test_run_prettier_on_syntax_error_file', 'git_dir_with_json_malformed', 'run_prettier_on_file', 'test_run_prettier_on_malformed_file']</t>
-  </si>
-  <si>
-    <t>[75, 76, 77, 78, 79, 80, 16, 43, 67, 79, 81, 82, 83, 84, 88, 89, 90, 91, 92, 97, 98, 620, 1026, 1029, 42, 62, 63, 64, 65]</t>
-  </si>
-  <si>
-    <t>https://github.com/nf-core/tools/compare/9974e0d1d65c36f0124fb8b557cafe2ed6e188c1...c98c5c7b3dbadac0034a23ee7fef18ba39503b62</t>
-  </si>
-  <si>
-    <t>9974e0d1d65c36f0124fb8b557cafe2ed6e188c1</t>
-  </si>
-  <si>
-    <t>c98c5c7b3dbadac0034a23ee7fef18ba39503b62</t>
-  </si>
-  <si>
     <t>marrink-lab/vermouth-martinize</t>
   </si>
   <si>
@@ -1879,10 +1174,10 @@
     <t>https://github.com/marrink-lab/vermouth-martinize/issues/203</t>
   </si>
   <si>
-    <t>['vermouth/processors/average_beads.py', 'vermouth/tests/test_average_beads.py']</t>
-  </si>
-  <si>
-    <t>['test_do_average_bead', 'test_processor_weight', 'mol_with_subgraph', 'do_average_bead', 'test_processor_variable']</t>
+    <t>['vermouth/tests/test_average_beads.py', 'vermouth/processors/average_beads.py']</t>
+  </si>
+  <si>
+    <t>['test_processor_weight', 'mol_with_subgraph', 'test_processor_variable', 'test_do_average_bead', 'do_average_bead']</t>
   </si>
   <si>
     <t>[80, 90, 91, 92, 93, 94, 95, 96, 97, 62, 63, 64, 65, 66, 67, 68, 69, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79, 80, 81, 82, 83, 84, 85, 116, 147, 157]</t>
@@ -1971,10 +1266,10 @@
     <t>https://github.com/marrink-lab/vermouth-martinize/issues/483</t>
   </si>
   <si>
-    <t>['vermouth/tests/test_molecule.py', 'vermouth/molecule.py']</t>
-  </si>
-  <si>
-    <t>['remove_matching_interaction', 'test_to_molecule', 'test_remove_interaction']</t>
+    <t>['vermouth/molecule.py', 'vermouth/tests/test_molecule.py']</t>
+  </si>
+  <si>
+    <t>['test_remove_interaction', 'remove_matching_interaction', 'test_to_molecule']</t>
   </si>
   <si>
     <t>[592, 599, 600, 1282, 1283, 1284, 1285, 1286, 1287, 1288, 1289, 1290, 1291, 1292, 1293, 1294, 1295, 1296, 1297, 1298, 1299, 1300, 1301, 1302, 1303, 1304, 1305, 1306, 1307, 1308, 1309, 1310, 1311, 1312, 1313, 1314, 1315, 1316, 1317, 1318, 1319, 1320, 1321, 1322, 1323, 1324, 1325, 1326, 1327, 1328, 1329, 1330, 1331, 1332, 1333, 1334, 1335, 1336]</t>
@@ -2000,7 +1295,7 @@
     <t>https://github.com/marrink-lab/vermouth-martinize/issues/433</t>
   </si>
   <si>
-    <t>['vermouth/gmx/gro.py', 'vermouth/pdb/pdb.py', 'pdb.py b/vermouth/pdb/pdb.py']</t>
+    <t>['pdb.py b/vermouth/pdb/pdb.py', 'vermouth/pdb/pdb.py', 'vermouth/gmx/gro.py']</t>
   </si>
   <si>
     <t>['write_gro', 'write_pdb']</t>
@@ -2016,6 +1311,563 @@
   </si>
   <si>
     <t>72972ec4bafaae6a2c736cf1c68d910b164ec1e6</t>
+  </si>
+  <si>
+    <t>databiosphere/toil</t>
+  </si>
+  <si>
+    <t>https://github.com/databiosphere/toil</t>
+  </si>
+  <si>
+    <t>AWS import/export test fails with 409 BucketAlreadyOwnedByYou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://jenkins.cgcloud.info/job/toil-pull-requests/1423/testReport/junit/src.toil.test.jobStores.jobStoreTest/EncryptedAWSJobStoreTest/test_importExportFile__size_partsize__otherJobStore_awsjobstoretest/
+Is this caused by a retry?
+</t>
+  </si>
+  <si>
+    <t>https://github.com/DataBiosphere/toil/issues/955</t>
+  </si>
+  <si>
+    <t>['src/toil/jobStores/aws/jobStore.py']</t>
+  </si>
+  <si>
+    <t>['AWSJobStore']</t>
+  </si>
+  <si>
+    <t>['_getOrCreateDomain', 'deleteJobStore', '__getBucketRegion']</t>
+  </si>
+  <si>
+    <t>[40, 53, 54, 524, 525, 526, 527, 528, 529, 530, 531, 533, 534, 535, 536, 537, 538, 539, 540, 541, 542, 543, 544, 545, 546, 547, 548, 549, 550, 551, 552, 553, 564, 1098, 1099, 1100, 1101, 1102]</t>
+  </si>
+  <si>
+    <t>https://github.com/databiosphere/toil/compare/ba6b80830ca9c6ddea3d72b5149896bb0c56c202...e17fe6e3d2c52953427919168e0fa2fd0b4fc653</t>
+  </si>
+  <si>
+    <t>ba6b80830ca9c6ddea3d72b5149896bb0c56c202</t>
+  </si>
+  <si>
+    <t>e17fe6e3d2c52953427919168e0fa2fd0b4fc653</t>
+  </si>
+  <si>
+    <t>Harbingerfile deletion race condition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">```
+l/k/jobIi7VIc:  Traceback (most recent call last):
+l/k/jobIi7VIc:    File "/home/alden/progressiveCactus3/python/local/lib/python2.7/site-packages/toil/worker.py", line 332, in main
+l/k/jobIi7VIc:      job._runner(jobWrapper=jobWrapper, jobStore=jobStore, fileStore=fileStore)
+l/k/jobIi7VIc:    File "/home/alden/progressiveCactus3/python/local/lib/python2.7/site-packages/toil/job.py", line 2323, in _runner
+l/k/jobIi7VIc:      returnValues = self._run(jobWrapper, fileStore)
+l/k/jobIi7VIc:    File "/home/alden/progressiveCactus3/python/local/lib/python2.7/site-packages/toil/job.py", line 2271, in _run
+l/k/jobIi7VIc:      return self.run(fileStore)
+l/k/jobIi7VIc:    File "/home/alden/progressiveCactus3/submodules/cactus/pipeline/cactus_workflow.py", line 900, in run
+l/k/jobIi7VIc:      self.cactusSequencesPath = fileStore.readGlobalFile(self.cactusSequencesID)
+l/k/jobIi7VIc:    File "/home/alden/progressiveCactus3/python/local/lib/python2.7/site-packages/toil/job.py", line 816, in readGlobalFile
+l/k/jobIi7VIc:      harbingerFile.waitOnDownload(lockFileHandle)
+l/k/jobIi7VIc:    File "/home/alden/progressiveCactus3/python/local/lib/python2.7/site-packages/toil/job.py", line 1603, in waitOnDownload
+l/k/jobIi7VIc:      pid = self.read()
+l/k/jobIi7VIc:    File "/home/alden/progressiveCactus3/python/local/lib/python2.7/site-packages/toil/job.py", line 1616, in read
+l/k/jobIi7VIc:      return int(open(self.harbingerFileName).read())
+l/k/jobIi7VIc:  IOError: [Errno 2] No such file or directory: '/tmp/toil-269fb642-c572-42a1-8c9f-aa751fa3e5e9/cache-269fb642-c572-42a1-8c9f-aa751fa3e5e9/.di9QL3RtcHo0d3RtVC50bXA=.harbinger'
+```
+I haven't fully investigated this yet, but it looks like the harbinger file can be deleted by the asyncWrite thread after self.exists() is checked but before self.read() is called in waitOnDownload(). Maybe HarbingerFile.delete() should acquire the cache lock? Also, should line https://github.com/BD2KGenomics/toil/blob/edf86b5e253e9003a441a68773e79ecaded1a599/src/toil/job.py#L1613 be self.delete() instead of harbingerFile.delete()?
+</t>
+  </si>
+  <si>
+    <t>https://github.com/DataBiosphere/toil/issues/1046</t>
+  </si>
+  <si>
+    <t>['src/toil/job.py']</t>
+  </si>
+  <si>
+    <t>['Job']</t>
+  </si>
+  <si>
+    <t>['read', '_delete', 'delete', 'write']</t>
+  </si>
+  <si>
+    <t>[855, 1579, 1583, 1584, 1614, 1623, 1624, 1625, 1626, 1627, 1628, 1629, 1630, 1631, 1632, 1633, 1634, 1635]</t>
+  </si>
+  <si>
+    <t>https://github.com/databiosphere/toil/compare/a671aab1dae99723e2bbd3239ad771b7d78fb9c4...270fdd5c0f13af54be0d564283720a3555129977</t>
+  </si>
+  <si>
+    <t>a671aab1dae99723e2bbd3239ad771b7d78fb9c4</t>
+  </si>
+  <si>
+    <t>270fdd5c0f13af54be0d564283720a3555129977</t>
+  </si>
+  <si>
+    <t>PromisedRequirement doesn't work with static DAGs defined in job functions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">```
+#!/usr/bin/env python2.7
+'''
+Author : Arjun Arkal Rao
+Affiliation : UCSC BME, UCSC Genomics Institute
+File : toy_code_for_unfulfilled_promise_error.py
+'''
+from __future__ import print_function
+from toil.job import Job, PromisedRequirement
+import argparse
+def test_test():
+    '''
+    '''
+    parser = argparse.ArgumentParser()
+    parser.add_argument('--dummy', dest='dummy', default=None, required=False)
+    Job.Runner.addToilOptions(parser)
+    params = parser.parse_args()
+    F1 = Job.wrapJobFn(returner, disk='100M')
+    F2 = Job.wrapJobFn(caller, F1.rv(), disk='200M')
+    F1.addChild(F2)
+    Job.Runner.startToil(F1, params)
+def returner(job):
+    job.fileStore.logToMaster(str(job.effectiveRequirements(job.fileStore.jobStore.config).disk))
+    return 10
+def caller(job, x):
+    G = job.wrapJobFn(returner, disk=PromisedRequirement(oop, x))
+    H = job.wrapJobFn(returner, disk=PromisedRequirement(lambda x: x, G.rv()))
+    job.addChild(G)
+    G.addChild(H)
+def oop(x):
+    return x + 1000
+if __name__ == '__main__':
+    test_test()
+```
+Gives an unpickling error
+```
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:54,817 INFO: toil.lib.bioio: Logging set at level: INFO
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:54,817 INFO: toil.lib.bioio: Logging set at level: INFO
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:54,822 INFO: toil.jobStores.fileJobStore: Jobstore directory is: /tmp/oppo
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:54,823 INFO: toil.jobStores.abstractJobStore: The workflow ID is: '6bd05e7c-68b1-4480-9d6e-63a3d8620fb1'
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:54,834 INFO: toil.common: Using the single machine batch system
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:54,834 WARNING: toil.batchSystems.singleMachine: Limiting maxCores to CPU count of system (4).
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:54,834 WARNING: toil.batchSystems.singleMachine: Limiting maxMemory to physically available memory (8589934592).
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:54,834 INFO: toil.batchSystems.singleMachine: Setting up the thread pool with 40 workers, given a minimum CPU fraction of 0.100000 and a maximum CPU value of 4.
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:54,841 INFO: toil.common: Written the environment for the jobs to the environment file
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:54,841 INFO: toil.common: Caching all jobs in job store
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:54,841 INFO: toil.common: 0 jobs downloaded.
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:54,846 INFO: toil.realtimeLogger: Real-time logging disabled
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:54,846 INFO: toil.leader: (Re)building internal scheduler state
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:54,847 INFO: toil.leader: Checked batch system has no running jobs and no updated jobs
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:54,847 INFO: toil.leader: Found 1 jobs to start and 0 jobs with successors to run
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:54,850 INFO: toil.leader: Starting the main loop
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:54,852 INFO: toil.batchSystems.singleMachine: Executing command: '/Users/arjun/cached_toil/toil/venv/bin/_toil_worker /tmp/oppo I/G/job79W4uy'.
+INFO:toil.common:Created the workflow directory at /tmp/toil-6bd05e7c-68b1-4480-9d6e-63a3d8620fb1
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,189 INFO: toil.batchSystems.singleMachine: Executing command: '/Users/arjun/cached_toil/toil/venv/bin/_toil_worker /tmp/oppo s/p/jobYpr2z2'.
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,355 INFO: toil.leader: Got message from job at time 07-03-2016 00:49:55: 104857600
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,415 INFO: toil.batchSystems.singleMachine: Executing command: '/Users/arjun/cached_toil/toil/venv/bin/_toil_worker /tmp/oppo 3/L/jobp7fI6l'.
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,417 INFO: toil.batchSystems.singleMachine: Executing command: '/Users/arjun/cached_toil/toil/venv/bin/_toil_worker /tmp/oppo o/Y/jobtB78cQ'.
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,649 WARNING: toil.leader: The jobWrapper seems to have left a log file, indicating failure: o/Y/jobtB78cQ
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,649 WARNING: toil.leader: Reporting file: o/Y/jobtB78cQ
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,649 WARNING: toil.leader: o/Y/jobtB78cQ:  ---TOIL WORKER OUTPUT LOG---
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,649 WARNING: toil.leader: o/Y/jobtB78cQ:  WARNING:toil.resource:The localize() method should only be invoked on a worker.
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,649 WARNING: toil.leader: o/Y/jobtB78cQ:  WARNING:toil.resource:Can't find resource for leader path '/Users/arjun/LUSC_scaling'
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,649 WARNING: toil.leader: o/Y/jobtB78cQ:  WARNING:toil.resource:Can't localize module ModuleDescriptor(dirPath='/Users/arjun/LUSC_scaling', name='pootest')
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,650 WARNING: toil.leader: o/Y/jobtB78cQ:  INFO:toil.jobStores.fileJobStore:Jobstore directory is: /tmp/oppo
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,650 WARNING: toil.leader: o/Y/jobtB78cQ:  Traceback (most recent call last):
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,650 WARNING: toil.leader: o/Y/jobtB78cQ:    File "/Users/arjun/cached_toil/toil/src/toil/worker.py", line 318, in main
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,650 WARNING: toil.leader: o/Y/jobtB78cQ:      job = Job._loadJob(jobWrapper.command, jobStore)
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,650 WARNING: toil.leader: o/Y/jobtB78cQ:    File "/Users/arjun/cached_toil/toil/src/toil/job.py", line 1911, in _loadJob
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,650 WARNING: toil.leader: o/Y/jobtB78cQ:      return cls._unpickle(userModule, fileHandle)
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,650 WARNING: toil.leader: o/Y/jobtB78cQ:    File "/Users/arjun/cached_toil/toil/src/toil/job.py", line 1934, in _unpickle
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,650 WARNING: toil.leader: o/Y/jobtB78cQ:      return unpickler.load()
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,650 WARNING: toil.leader: o/Y/jobtB78cQ:  EOFError
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,650 WARNING: toil.leader: o/Y/jobtB78cQ:  Exiting the worker because of a failed jobWrapper on host Arjuns-MacBook-Pro.local
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,650 WARNING: toil.leader: o/Y/jobtB78cQ:  ERROR:toil.worker:Exiting the worker because of a failed jobWrapper on host Arjuns-MacBook-Pro.local
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,651 WARNING: toil.leader: o/Y/jobtB78cQ:  WARNING:toil.jobWrapper:Due to failure we are reducing the remaining retry count of job o/Y/jobtB78cQ to 0
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,651 WARNING: toil.leader: Job: o/Y/jobtB78cQ is completely failed
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,858 INFO: toil.leader: Got message from job at time 07-03-2016 00:49:55: 1010
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:55,859 INFO: toil.leader: Got message from job at time 07-03-2016 00:49:55: Added file with ID 's/N/tmpVn48W4.tmp' to the list of files to be globally deleted.
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:57,654 INFO: toil.leader: No jobs left to run so exiting.
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:57,655 INFO: toil.leader: Finished the main loop
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:57,655 INFO: toil.leader: Waiting for stats and logging collator process to finish ...
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:57,870 INFO: toil.leader: ... finished collating stats and logs. Took 0.214813947678 seconds
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:57,870 INFO: toil.leader: Waiting for service manager thread to finish ...
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:58,857 INFO: toil.leader: ... finished shutting down the service manager. Took 0.986219882965 seconds
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:58,857 INFO: toil.leader: Finished toil run with 3 failed jobs
+Arjuns-MacBook-Pro.local: 2016-07-03 00:49:58,857 INFO: toil.leader: Failed jobs at end of the run: set(['s/p/jobYpr2z2', 'o/Y/jobtB78cQ', 'I/G/job79W4uy'])
+Traceback (most recent call last):
+  File "/Users/arjun/LUSC_scaling/pootest.py", line 44, in &lt;module&gt;
+    test_test()
+  File "/Users/arjun/LUSC_scaling/pootest.py", line 24, in test_test
+    Job.Runner.startToil(F1, params)
+  File "/Users/arjun/cached_toil/toil/src/toil/job.py", line 515, in startToil
+    return toil.start(job)
+  File "/Users/arjun/cached_toil/toil/src/toil/common.py", line 546, in start
+    return self._runMainLoop(job)
+  File "/Users/arjun/cached_toil/toil/src/toil/common.py", line 756, in _runMainLoop
+    jobCache=self._jobCache)
+  File "/Users/arjun/cached_toil/toil/src/toil/leader.py", line 694, in mainLoop
+    raise FailedJobsException( config.jobStore, len(toilState.totalFailedJobs) )
+toil.leader.FailedJobsException: The job store '/tmp/oppo' contains 3 failed jobs
+```
+On the plus side, functions can be passed to PromisedRequirement, the second call (function H) fails whether its a lambda or a function.
+@jpfeil @hannes-ucsc can you look at this?
+*As always pay no attention to the names of my files lol.
+</t>
+  </si>
+  <si>
+    <t>https://github.com/DataBiosphere/toil/issues/1039</t>
+  </si>
+  <si>
+    <t>['src/toil/test/src/promisedRequirementTest.py', 'src/toil/job.py']</t>
+  </si>
+  <si>
+    <t>['SingleMachinePromisedRequirementsTest', 'MesosPromisedRequirementsTest', 'EncapsulatedJob', 'Job', 'PromisedRequirementFunctionWrappingJob', 'PromisedRequirementJobFunctionWrappingJob']</t>
+  </si>
+  <si>
+    <t>['evaluatePromisedRequirements', 'testJobConcurrency', 'testConcurrencyStatic', 'tearDown', '_writer', 'create', 'maxConcurrency', 'getThirtyTwoMb', '__init__', 'logDiskUsage', 'addChild', '_follower', 'testConcurrencyDynamic', 'run', 'testPromiseRequirementRaceStatic']</t>
+  </si>
+  <si>
+    <t>[57, 212, 227, 243, 259, 276, 293, 2454, 2457, 2458, 2459, 2462, 2463, 2464, 2465, 2466, 2467, 2468, 2469, 2470, 2471, 2472, 2477, 2481, 2484, 2485, 2487, 2499, 2523, 2524, 2527, 2528, 18, 41, 55, 118, 123, 127, 128, 129, 130, 131, 132, 133, 134, 135, 136, 194, 195, 196, 197, 198, 199, 200, 201, 202, 203, 204, 205, 230]</t>
+  </si>
+  <si>
+    <t>https://github.com/databiosphere/toil/compare/0a613b719b8b22537ee349f671d51260057c2cf4...38b155d6c4b9dd1613b9d0ca5c497ba1ed05ef87</t>
+  </si>
+  <si>
+    <t>0a613b719b8b22537ee349f671d51260057c2cf4</t>
+  </si>
+  <si>
+    <t>38b155d6c4b9dd1613b9d0ca5c497ba1ed05ef87</t>
+  </si>
+  <si>
+    <t>logToMaster() doesn't work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is an example from the docs. It does not print the logToMaster() message, neither on master nor on 3.1.x.
+```
+from toil.job import Job
+class HelloWorld(Job):
+    def __init__(self, message):
+        Job.__init__(self,  memory="2G", cores=2, disk="3G")
+        self.message = message
+    def run(self, fileStore):
+        fileStore.logToMaster("Hello, world!, I have a message: %s"
+                              % self.message)
+if __name__=="__main__":
+    options = Job.Runner.getDefaultOptions("./toilWorkflowRun")
+    options.logLevel = "INFO"
+    Job.Runner.startToil(HelloWorld("woot"), options)
+```
+</t>
+  </si>
+  <si>
+    <t>https://github.com/DataBiosphere/toil/issues/683</t>
+  </si>
+  <si>
+    <t>['src/toil/worker.py', 'src/toil/leader.py']</t>
+  </si>
+  <si>
+    <t>['statsAndLoggingAggregatorProcess', 'callback', 'main']</t>
+  </si>
+  <si>
+    <t>[48, 395, 396, 397]</t>
+  </si>
+  <si>
+    <t>https://github.com/databiosphere/toil/compare/ed656894745f0ec138c19fbf5860a40dddff9532...c751e938eca21a966e31716483d5eb22c20972c9</t>
+  </si>
+  <si>
+    <t>ed656894745f0ec138c19fbf5860a40dddff9532</t>
+  </si>
+  <si>
+    <t>c751e938eca21a966e31716483d5eb22c20972c9</t>
+  </si>
+  <si>
+    <t>Global name 'config' not defined for getting azure job store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`global name 'config' is not defined` error found in `toil/common.py` on line 617 in `getJobStore` when running toil version 3.3.1 on an Azure cluster. Error does not show up for toil version 3.2.1 and the toil script runs to completion. File `.toilAzureCredentials` is set properly.
+Toil script command:
+`./vg_evaluation_pipeline.py --batchSystem mesos --mesosMaster 10.0.0.5:5050 --realTimeLogging --logError --logDebug --edge_max 5 --kmer_size 16 --index_mode gcsa-mem --include_primary 'azure:hgvm:hgvmeval-jobstore33' --path_name 'ref' --path_size 81189 '/home/cmarkello/debug_eval_input/BRCA1.vg' '/home/cmarkello/debug_eval_input/BRCA1/NA12877/NA12877.bam.fq' 'NA12877' '/home/cmarkello/debug_eval_output' 'azure:hgvm:hgvmdebugtest-input' 'azure:hgvm:hgvmdebugtest-output'`
+Toil script `main(args)` function:
+`
+```
+if len(args) == 2 and args[1] == "--test":
+    # Run the tests
+    return doctest.testmod(optionflags=doctest.NORMALIZE_WHITESPACE)
+RealTimeLogger.start_master()
+options = parse_args(args) # This holds the nicely-parsed options object
+with Toil(options) as toil:
+    if not toil.options.restart:
+        # Upload local files to the remote IO Store
+        inputGraphFileID = toil.importFile('file://'+options.vg_graph)
+        inputReadsFileID = toil.importFile('file://'+options.sample_reads)
+        uploadList = [[inputGraphFileID, options.vg_graph], [inputReadsFileID, options.sample_reads]]
+        # Make a root job
+        root_job = Job.wrapJobFn(run_upload, options, uploadList, cores=2, memory="5G", disk="5G")
+        # Run the job and store the returned list of output files to download
+        outputFileIDList = toil.start(root_job)
+    else:
+        outputFileIDList = toil.restart()
+    # Download output files to the local machine that runs this script
+    run_download(toil, options, outputFileIDList)
+print("All jobs completed successfully")
+RealTimeLogger.stop_master()`
+```
+</t>
+  </si>
+  <si>
+    <t>https://github.com/DataBiosphere/toil/issues/1097</t>
+  </si>
+  <si>
+    <t>['src/toil/common.py']</t>
+  </si>
+  <si>
+    <t>['Toil']</t>
+  </si>
+  <si>
+    <t>[636]</t>
+  </si>
+  <si>
+    <t>https://github.com/databiosphere/toil/compare/e6e8cfae815bbed7a43897dad8e8177cb49012d8...783f958e75553178c42ef4e9ab6d052723accf08</t>
+  </si>
+  <si>
+    <t>e6e8cfae815bbed7a43897dad8e8177cb49012d8</t>
+  </si>
+  <si>
+    <t>783f958e75553178c42ef4e9ab6d052723accf08</t>
+  </si>
+  <si>
+    <t>faucetsdn/faucet</t>
+  </si>
+  <si>
+    <t>https://github.com/faucetsdn/faucet</t>
+  </si>
+  <si>
+    <t>Updating config variables for some dp variables won't send flow mods (change won't be reflected)</t>
+  </si>
+  <si>
+    <t>Updating most config variables (excluding ones that will force a cold restart such as dot1x) won't send a correct flowmod when sighup is sent._x000D_
+_x000D_
+Some examples are _x000D_
+_x000D_
+drop_broadcast_source_address, drop_spoofed_faucet_mac, priority_offset, packetin_pps...etc._x000D_
+_x000D_
+Guessing this happens because dp cold start doesn't happen when these values are changed, and warm start won't trigger changes to these variables.</t>
+  </si>
+  <si>
+    <t>https://github.com/faucetsdn/faucet/issues/3420</t>
+  </si>
+  <si>
+    <t>['clib/mininet_test_base.py', 'tests/unit/faucet/test_valve_config.py', 'tests/unit/faucet/test_valve_stack.py', 'faucet/conf.py', 'tests/unit/faucet/test_config.py', 'mininet_test_base.py b/clib/mininet_test_base.py', 'faucet/valve_host.py', 'faucet/dp.py', 'faucet/port.py', 'faucet/valve.py', 'tests/integration/mininet_tests.py', 'faucet/valves_manager.py']</t>
+  </si>
+  <si>
+    <t>['ValveHostManager', 'ValvesManager', 'ValveACLTestCase', 'FaucetConfigReloadTest', 'InvalidConfigError', 'ValveTestConfigRevertBootstrap', 'ValveAddVLANTestCase', 'Port', 'ValveAddPortTestCase', 'ValveStackGraphUpdateTestCase', 'ValveChangeDPTestCase', 'Conf', 'Valve']</t>
+  </si>
+  <si>
+    <t>['_get_meter_config_changes', 'test_config_condition', 'get_config_changes', 'force_faucet_reload', 'test_port_add', 'get_node_link_data', 'ignore_subconf', '_get_acl_config_changes', '__init__', '_get_port_config_changes', 'shortest_path_to_root', 'test_port_delete', '_add_changed_vlan_port', 'get_tables', 'datapath_connect', 'check_config', '__setattr__', '__eq__', 'stack_longest_path_to_root_len', 'conf_hash', 'conf_diff', '__hash__', 'to_conf', '_conf_keys', '_table_configs', 'test_change_dp', 'setUp']</t>
+  </si>
+  <si>
+    <t>[2083, 39, 40, 57, 119, 120, 122, 124, 127, 130, 131, 132, 133, 134, 166, 175, 178, 183, 209, 210, 211, 225, 332, 866, 880, 884, 888, 922, 923, 924, 925, 926, 1356, 1357, 1359, 1360, 1391, 1392, 1422, 1429, 1435, 1436, 1438, 1447, 1448, 1450, 1452, 1453, 1454, 1455, 1459, 1461, 1462, 1463, 1464, 1465, 1466, 1467, 1468, 1469, 1470, 1471, 1472, 1473, 1474, 1475, 1476, 1477, 1478, 1479, 1480, 1481, 1482, 1483, 1484, 1485, 1486, 1487, 1491, 1492, 1493, 1494, 1495, 1496, 1497, 1498, 1519, 1520, 1521, 1522, 1523, 1524, 1525, 1526, 1527, 1528, 1529, 1530, 1532, 1549, 1550, 1551, 1562, 1563, 1571, 1575, 1576, 1577, 1578, 1584, 1585, 1586, 1587, 1592, 136, 174, 189, 205, 232, 664, 668, 1032, 1472, 1760, 1761, 1775, 1839, 1840, 29, 47, 245, 251, 365, 3131, 184, 183, 229, 335, 336, 337, 338, 339, 340, 341, 342, 343, 344, 345, 346, 347, 348, 349, 350, 351, 352, 353, 354, 355, 356, 357, 358, 359, 360, 361, 362, 363, 364, 365, 366, 367, 368, 369, 370, 371, 372, 373, 535, 536, 537, 551, 552, 553, 579</t>
+  </si>
+  <si>
+    <t>https://github.com/faucetsdn/faucet/compare/092fe74adbcb9c363948cbaf160c4a970b29f4e0...ac68a5f5963a0366ace9d31aa3789bfff1de9005</t>
+  </si>
+  <si>
+    <t>092fe74adbcb9c363948cbaf160c4a970b29f4e0</t>
+  </si>
+  <si>
+    <t>ac68a5f5963a0366ace9d31aa3789bfff1de9005</t>
+  </si>
+  <si>
+    <t>Moving host from one port to another doesn't trigger EXPIRE/LEARN events</t>
+  </si>
+  <si>
+    <t>I plugged a device into port 6, and Faucet L2 learned it, then I unplugged it and plugged it into port 8, where I would have expected an L2 expire on port 6, and then an L2 learn on port 8, but instead don't see either. Is this the expected behavior?_x000D_
+_x000D_
+```_x000D_
+Dec 26 19:43:44 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 Configuring VLAN demo vid:10 untagged: Port 1,Port 2,Port 3,Port 4,Port 5,Port 6,Port 7,Port 8,Port 9,Port 10,Port 11,Port 12,Port 13,Port 14,Port 15,Port 16,Port 17,Port 18,Port 19,Port 20,Port 21,Port 22,Port 24_x000D_
+Dec 26 19:43:46 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 L2 learned on Port 6 00:1a:eb:dd:bd:e0 (L2 type 0x0800, L2 dst ff:ff:ff:ff:ff:ff, L3 src 0.0.0.0, L3 dst 255.255.255.255) Port 6 VLAN 10 (26 hosts total)_x000D_
+Dec 26 19:43:56 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 L2 learned on Port 24 c8:f7:33:db:2d:8d (L2 type 0x0800, L2 dst 01:00:5e:7f:ff:fa, L3 src 192.168.0.43, L3 dst 239.255.255.250) Port 24 VLAN 10 (26 hosts total)_x000D_
+Dec 26 19:44:01 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 L2 learned on Port 24 d0:73:d5:57:0d:2e (L2 type 0x0806, L2 dst ff:ff:ff:ff:ff:ff, L3 src 192.168.0.4, L3 dst 192.168.0.4) Port 24 VLAN 10 (26 hosts total)_x000D_
+Dec 26 19:44:05 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 L2 learned on Port 24 d0:73:d5:3d:21:f7 (L2 type 0x0806, L2 dst ff:ff:ff:ff:ff:ff, L3 src 192.168.0.14, L3 dst 192.168.0.14) Port 24 VLAN 10 (26 hosts total)_x000D_
+Dec 26 19:44:15 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 L2 learned on Port 24 6c:40:08:8c:80:98 (L2 type 0x0800, L2 dst ff:ff:ff:ff:ff:ff, L3 src 192.168.0.55, L3 dst 192.168.0.255) Port 24 VLAN 10 (26 hosts total)_x000D_
+Dec 26 19:44:21 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 24 recently active hosts on VLAN 10, expired [d0:73:d5:41:7b:8a on Port 24, d0:73:d5:2d:b8:f5 on Port 24]_x000D_
+Dec 26 19:44:25 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 L2 learned on Port 24 d0:73:d5:41:7b:8a (L2 type 0x0800, L2 dst 01:00:5e:00:00:fb, L3 src 192.168.0.20, L3 dst 224.0.0.251) Port 24 VLAN 10 (25 hosts total)_x000D_
+Dec 26 19:44:27 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 L2 learned on Port 24 d0:73:d5:2d:b8:f5 (L2 type 0x0800, L2 dst 01:00:5e:00:00:fb, L3 src 192.168.0.22, L3 dst 224.0.0.251) Port 24 VLAN 10 (26 hosts total)_x000D_
+Dec 26 19:44:27 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 L2 learned on Port 24 d0:73:d5:2d:9d:e1 (L2 type 0x0800, L2 dst 01:00:5e:00:00:fb, L3 src 192.168.0.12, L3 dst 224.0.0.251) Port 24 VLAN 10 (26 hosts total)_x000D_
+Dec 26 19:44:27 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 L2 learned on Port 24 68:5b:35:c9:76:15 (L2 type 0x0800, L2 dst 00:1f:c6:9c:d2:dd, L3 src 192.168.0.46, L3 dst 192.168.0.48) Port 24 VLAN 10 (26 hosts total)_x000D_
+Dec 26 19:45:02 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 25 recently active hosts on VLAN 10, expired [d0:73:d5:40:ba:95 on Port 24]_x000D_
+Dec 26 19:45:13 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 L2 learned on Port 24 d0:73:d5:3d:86:9a (L2 type 0x0806, L2 dst ff:ff:ff:ff:ff:ff, L3 src 192.168.0.11, L3 dst 192.168.0.11) Port 24 VLAN 10 (25 hosts total)_x000D_
+Dec 26 19:45:24 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 L2 learned on Port 2 00:1f:c6:9b:c2:05 (L2 type 0x0806, L2 dst 8c:59:73:26:49:91, L3 src 192.168.0.67, L3 dst 192.168.0.1) Port 2 VLAN 10 (25 hosts total)_x000D_
+Dec 26 19:45:58 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 Port 6 up status False reason MODIFY state 1_x000D_
+Dec 26 19:45:58 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 Port 6 (6) down_x000D_
+Dec 26 19:46:01 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 Port 8 up status True reason MODIFY state 0_x000D_
+Dec 26 19:46:01 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 Port 8 (8) up_x000D_
+Dec 26 19:46:01 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 Configuring VLAN demo vid:10 untagged: Port 1,Port 2,Port 3,Port 4,Port 5,Port 6,Port 7,Port 8,Port 9,Port 10,Port 11,Port 12,Port 13,Port 14,Port 15,Port 16,Port 17,Port 18,Port 19,Port 20,Port 21,Port 22,Port 24_x000D_
+Dec 26 19:46:12 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 L2 learned on Port 24 8c:59:73:26:49:91 (L2 type 0x0806, L2 dst ff:ff:ff:ff:ff:ff, L3 src 192.168.0.1, L3 dst 192.168.0.29) Port 24 VLAN 10 (24 hosts total)_x000D_
+Dec 26 19:46:16 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 L2 learned on Port 24 d0:73:d5:40:ba:95 (L2 type 0x0800, L2 dst 01:00:5e:00:00:fb, L3 src 192.168.0.21, L3 dst 224.0.0.251) Port 24 VLAN 10 (25 hosts total)_x000D_
+Dec 26 19:46:38 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 L2 learned on Port 22 00:e0:4c:68:17:14 (L2 type 0x0800, L2 dst 8c:59:73:26:49:91, L3 src 192.168.0.98, L3 dst 205.171.3.25) Port 22 VLAN 10 (25 hosts total)_x000D_
+Dec 26 19:46:43 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 L2 learned on Port 24 7c:10:15:00:f4:d2 (L2 type 0x0806, L2 dst ff:ff:ff:ff:ff:ff, L3 src 192.168.0.36, L3 dst 192.168.0.13) Port 24 VLAN 10 (25 hosts total)_x000D_
+Dec 26 19:47:33 faucet.valve INFO     DPID 260367057655831 (0xeccd6dfb9817) x510 24 recently active hosts on VLAN 10, expired [d0:73:d5:2d:9a:12 on Port 24]_x000D_
+```</t>
+  </si>
+  <si>
+    <t>https://github.com/faucetsdn/faucet/issues/3400</t>
+  </si>
+  <si>
+    <t>['faucet/faucet.py', 'faucet/valve_host.py', 'faucet/port.py', 'tests/integration/mininet_tests.py', 'faucet/valve_flood.py', 'faucet/valve.py', 'faucet/valves_manager.py', 'tests/unit/faucet/valve_test_lib.py']</t>
+  </si>
+  <si>
+    <t>['ValveFloodManager', 'ValveHostManager', 'ValvesManager', 'FaucetUntaggedHostMoveTest', 'FaucetUntaggedHostPermanentLearnTest', 'ValveTestBases', 'Port', 'ValveFloodStackManagerBase', 'Valve', 'Faucet']</t>
+  </si>
+  <si>
+    <t>['_coprocessor_flows', 'advertise', '_set_port_status', 'port_delete', 'lacp_down', 'port_status_handler', 'update_stack_topo', 'test_untagged', 'set_port_down', 'test_unknown_port_status', 'test_move_port', 'ports_delete', '_reset_lacp_status', '_add_ports_and_vlans', '_port_delete_flows_state', 'set_port_up', 'valve_packet_in', 'flap_port']</t>
+  </si>
+  <si>
+    <t>[329, 210, 395, 406, 426, 437, 439, 459, 475, 476, 477, 478, 479, 480, 481, 482, 483, 484, 485, 486, 487, 489, 490, 491, 492, 493, 494, 495, 496, 497, 498, 626, 627, 628, 629, 630, 631, 647, 648, 714, 782, 788, 789, 915, 947, 954, 956, 962, 301, 541, 547, 548, 550, 322, 323, 324, 325, 325, 328, 3599, 3601, 3602, 3603, 3604, 3605, 3606, 3607, 3608, 3609, 3610, 3611, 31, 654, 660, 1648, 1656]</t>
+  </si>
+  <si>
+    <t>https://github.com/faucetsdn/faucet/compare/67b9feeb4b5f37d76e93a229af20e0d8e5f026dc...396ae5154bc0905305561b12ba050f7e569d0bfe</t>
+  </si>
+  <si>
+    <t>67b9feeb4b5f37d76e93a229af20e0d8e5f026dc</t>
+  </si>
+  <si>
+    <t>396ae5154bc0905305561b12ba050f7e569d0bfe</t>
+  </si>
+  <si>
+    <t>Generative test failure</t>
+  </si>
+  <si>
+    <t>Raw logs here: https://github.com/faucetsdn/faucet/runs/969109880_x000D_
+_x000D_
+```_x000D_
+ERROR: test_G1044 (__main__.ValveTopologyTableTest)_x000D_
+Setup &amp; test topology_x000D_
+----------------------------------------------------------------------_x000D_
+Traceback (most recent call last):_x000D_
+  File "./test_topology.py", line 203, in test_x000D_
+    self.set_up(param)_x000D_
+  File "./test_topology.py", line 165, in set_up_x000D_
+    self.verify_traversal()_x000D_
+  File "./test_topology.py", line 196, in verify_traversal_x000D_
+    self.network.is_output(match, int(src_dpid), int(dst_dpid), port=dst_port)_x000D_
+  File "/faucet-src/clib/fakeoftable.py", line 163, in is_output_x000D_
+    priority = self.shortest_path_len(src_dpid, dst_dpid)_x000D_
+  File "/faucet-src/clib/fakeoftable.py", line 140, in shortest_path_len_x000D_
+    return len(src_valve.dp.shortest_path(dst_valve.dp.name))_x000D_
+AttributeError: 'DP' object has no attribute 'shortest_path'_x000D_
+```</t>
+  </si>
+  <si>
+    <t>https://github.com/faucetsdn/faucet/issues/3657</t>
+  </si>
+  <si>
+    <t>['clib/fakeoftable.py', 'fakeoftable.py b/clib/fakeoftable.py']</t>
+  </si>
+  <si>
+    <t>['FakeOFNetwork']</t>
+  </si>
+  <si>
+    <t>['is_output']</t>
+  </si>
+  <si>
+    <t>[140, 141, 142, 143, 144, 145]</t>
+  </si>
+  <si>
+    <t>https://github.com/faucetsdn/faucet/compare/007c76c48e3c8d97cc0900127f721ebdbce5b139...0818b8cf3d67cf9acf5de470afd728affc5ddcf1</t>
+  </si>
+  <si>
+    <t>007c76c48e3c8d97cc0900127f721ebdbce5b139</t>
+  </si>
+  <si>
+    <t>0818b8cf3d67cf9acf5de470afd728affc5ddcf1</t>
+  </si>
+  <si>
+    <t>New MC-LAG implementation doesn't work after cold start</t>
+  </si>
+  <si>
+    <t>Steps to reproduce:_x000D_
+_x000D_
+    1. Bring standby LAG port down_x000D_
+    2. Cold-start switch (either by bringing switch down and back up again, or reloading faucet with enough of a config change that it will cold start switches on the network)_x000D_
+    3. Bring standby LAG port up_x000D_
+_x000D_
+It never recognizes that the port is back up for whatever reason.  The dreaded cold-start cached state!  After this point, something about the LACP state machine seems to be borked, since I can't get it to recover with any sequence of bringing ports up/down, but restarting Faucet does fix the situation. _x000D_
+_x000D_
+```_x000D_
+&lt;cold start with sw2-28 down&gt;_x000D_
+Feb 10 19:19:14 faucet.valve INFO     DPID 178 (0xb2) nz-kiwi-t1sw2 Cold start configuring DP_x000D_
+Feb 10 19:19:14 faucet.valve INFO     DPID 178 (0xb2) nz-kiwi-t1sw2 Port 9 (to t2sw1 port 52) configured_x000D_
+Feb 10 19:19:14 faucet.valve INFO     DPID 178 (0xb2) nz-kiwi-t1sw2 Port 10 (to t2sw2 port 52) configured_x000D_
+Feb 10 19:19:14 faucet.valve INFO     DPID 178 (0xb2) nz-kiwi-t1sw2 Port 11 (to t2sw3 port 52) configured_x000D_
+Feb 10 19:19:14 faucet.valve INFO     DPID 178 (0xb2) nz-kiwi-t1sw2 Port 6 (to t1sw1 port 6) configured_x000D_
+Feb 10 19:19:14 faucet.valve INFO     DPID 178 (0xb2) nz-kiwi-t1sw2 Configuring VLAN 171 vid:171 tagged: Port 28_x000D_
+&lt;bring sw2-28 up&gt;_x000D_
+Feb 10 19:20:25 faucet.valve INFO     DPID 178 (0xb2) nz-kiwi-t1sw2 status change: Port 28 up status True reason MODIFY state 4_x000D_
+Feb 10 19:20:25 faucet.valve INFO     DPID 178 (0xb2) nz-kiwi-t1sw2 Port 28 (egress) up_x000D_
+Feb 10 19:20:25 faucet.valve INFO     DPID 178 (0xb2) nz-kiwi-t1sw2 Configuring VLAN 171 vid:171 tagged: Port 28_x000D_
+Feb 10 19:20:26 faucet.valve INFO     DPID 178 (0xb2) nz-kiwi-t1sw2 status did not change: Port 28 up status True reason MODIFY state 4_x000D_
+&lt;bring sw1-28 down&gt;_x000D_
+Feb 10 19:21:04 faucet.valve INFO     DPID 177 (0xb1) nz-kiwi-t1sw1 status did not change: Port 28 up status True reason MODIFY state 0_x000D_
+Feb 10 19:21:04 faucet.valve INFO     DPID 177 (0xb1) nz-kiwi-t1sw1 Port 28 state OFPPS_LIVE reset, ignoring in expectation of port down_x000D_
+Feb 10 19:21:04 faucet.valve INFO     DPID 177 (0xb1) nz-kiwi-t1sw1 status change: Port 28 up status False reason MODIFY state 1_x000D_
+Feb 10 19:21:04 faucet.valve INFO     DPID 177 (0xb1) nz-kiwi-t1sw1 Port 28 (egress) down_x000D_
+Feb 10 19:21:04 faucet.valve INFO     DPID 177 (0xb1) nz-kiwi-t1sw1 LAG 3 Port 28 actor state INITIALIZING (previous state UP)_x000D_
+Feb 10 19:21:04 faucet.valve INFO     DPID 177 (0xb1) nz-kiwi-t1sw1 LAG 3 Port 28 UNSELECTED (previous state SELECTED)_x000D_
+Feb 10 19:21:04 faucet.valve INFO     DPID 177 (0xb1) nz-kiwi-t1sw1 Configuring VLAN 171 vid:171 tagged: Port 28_x000D_
+```</t>
+  </si>
+  <si>
+    <t>https://github.com/faucetsdn/faucet/issues/3460</t>
+  </si>
+  <si>
+    <t>['faucet/valve.py', 'tests/integration/mininet_multidp_tests.py']</t>
+  </si>
+  <si>
+    <t>['FaucetSingleLAGOnUniqueVLANTest', 'Valve', 'FaucetSingleLAGTest']</t>
+  </si>
+  <si>
+    <t>['restart_on_down_lag_port', 'test_mclag_coldstart', 'test_mclag_warmstart']</t>
+  </si>
+  <si>
+    <t>[218, 220, 1073, 4, 1113, 1114, 1115, 1116, 1117, 1118, 1119, 1120, 1121, 1122, 1123, 1124, 1125, 1126, 1127, 1128, 1129, 1130, 1131, 1132, 1133, 1134, 1135, 1136, 1137, 1138, 1139, 1140, 1141, 1142, 1143, 1144, 1145, 1146, 1147, 1148, 1149, 1150, 1151, 1152, 1153, 1154, 1155, 1156, 1157, 1158, 1159, 1160, 1161, 1162, 1163, 1164, 1165, 1166, 1167, 1168]</t>
+  </si>
+  <si>
+    <t>https://github.com/faucetsdn/faucet/compare/dc8f363d107d962d142169930bcaab68ec764e5a...3cc160b0b22c64598e31ef7bac95b8ad88be342b</t>
+  </si>
+  <si>
+    <t>dc8f363d107d962d142169930bcaab68ec764e5a</t>
+  </si>
+  <si>
+    <t>3cc160b0b22c64598e31ef7bac95b8ad88be342b</t>
+  </si>
+  <si>
+    <t>When multi DP routing on stacking, FAUCET router can't resolve hosts on non-root DPs (because route resolver doesn't flood to stack ports)</t>
+  </si>
+  <si>
+    <t>See also._x000D_
+_x000D_
+https://github.com/faucetsdn/faucet/pull/3226</t>
+  </si>
+  <si>
+    <t>https://github.com/faucetsdn/faucet/issues/3227</t>
+  </si>
+  <si>
+    <t>['faucet/valve_route.py', 'faucet/valve_flood.py', 'faucet/valve.py', 'tests/unit/faucet/test_valve_stack.py']</t>
+  </si>
+  <si>
+    <t>['ValveFloodStackManagerNoReflection', 'ValveInterVLANStackFlood', 'ValveRouteManager', 'ValveStackChainTest', 'ValveTestIPV6StackedRouting', 'ValveFloodStackManagerBase', 'ValveStackRedundancyTestCase', 'ValveStackAndNonStackTestCase', 'ValveTestTunnel', 'ValveStackRedundantLink', 'ValveStackNonRootExtLoopProtectTestCase', 'ValveStackGraphBreakTestCase', 'ValveRootStackTestCase', 'ValveEdgeStackTestCase', 'Valve']</t>
+  </si>
+  <si>
+    <t>['_gw_respond_pkt', '_resolve_gw_on_port', 'test_flood_towards_root_from_s1', 'test_redundancy', 'test_topo', 'create_config', 'test_flood_towards_root_from_s4', 'test_loop_protect', 'get_other_valves', '__init__', 'test_flood_towards_root_from_s3', 'flood_manager_flood_ports', 'dp_by_name', 'route_manager_ofmsgs', '_set_max_lldp_lost', '_resolve_gw_on_vlan', '_stack_flood_ports', 'test_stack_learn_root', 'base_config', 'test_stack_learn_edge', 'test_nonstack_dp_port', 'set_stack_all_ports_status', 'test_flood_away_from_root', 'test_dpid_nominations', '_flood_stack_links', 'setUp']</t>
+  </si>
+  <si>
+    <t>[196, 197, 198, 199, 200, 201, 202, 203, 204, 205, 206, 207, 208, 209, 210, 211, 212, 213, 214, 215, 216, 217, 218, 219, 220, 221, 654, 655, 656, 657, 658, 659, 660, 661, 662, 663, 664, 665, 666, 667, 668, 669, 670, 671, 672, 673, 674, 675, 676, 677, 678, 679, 680, 681, 682, 683, 684, 685, 686, 687, 688, 689, 690, 691, 692, 693, 694, 695, 696, 697, 698, 699, 700, 701, 702, 703, 704, 705, 706, 113, 127, 145, 175, 176, 177, 178, 179, 180, 181, 182, 183, 184, 185, 186, 187, 188, 189, 190, 191, 194, 195, 196, 197, 198, 199, 200, 203, 204, 205, 22, 92, 93, 94, 95, 107, 124, 151, 169, 182, 200, 217, 370, 375, 513, 574, 594, 639, 652, 659, 665, 748, 798, 911, 1121, 1122, 1123, 1124, 1125, 1126, 1127, 1128, 1129, 1130, 1131, 1132, 1133, 1134, 1135, 1136, 1137, 1138, 1139, 1140, 1141, 1142, 1143, 1144, 1145, 1146, 1147, 1148, 1149, 1150, 1151, 1152, 1153, 1154, 1155, 1156, 1157, 1158, 1159, 1160, 1161, 1162, 1163, 1164, 1165, 1166, 1167, 1168, 1169, 1170, 1171, 1172, 1173, 1174, 1175, 1176, 117</t>
+  </si>
+  <si>
+    <t>https://github.com/faucetsdn/faucet/compare/ae3f2acdd06620ff84577aab72e9e3d6d3f56ee8...ec13ef611445ed4b40bb55a0989e661c7c204e76</t>
+  </si>
+  <si>
+    <t>ae3f2acdd06620ff84577aab72e9e3d6d3f56ee8</t>
+  </si>
+  <si>
+    <t>ec13ef611445ed4b40bb55a0989e661c7c204e76</t>
   </si>
   <si>
     <t>java</t>
@@ -2075,10 +1927,10 @@
     <t>['auth0/src/test/java/com/auth0/android/provider/CustomTabsControllerTest.java', 'auth0/src/main/java/com/auth0/android/provider/CustomTabsController.java']</t>
   </si>
   <si>
-    <t>['CustomTabsControllerTest', 'CustomTabsController']</t>
-  </si>
-  <si>
-    <t>['bindService', 'result', 'shouldUnbindEvenIfNotBound', 'unbindService']</t>
+    <t>['CustomTabsController', 'CustomTabsControllerTest']</t>
+  </si>
+  <si>
+    <t>['bindService', 'unbindService', 'shouldUnbindEvenIfNotBound', 'result']</t>
   </si>
   <si>
     <t>[34, 70, 71, 73, 74, 76, 85, 87, 96, 101]</t>
@@ -2152,7 +2004,7 @@
     <t>['CredentialsManager', 'CredentialsManagerTest']</t>
   </si>
   <si>
-    <t>['Date', 'shouldGetNonExpiredCredentialsFromStorage', 'CredentialsManagerException', 'shouldNotFailOnGetCredentialsWhenCacheExpiresAtNotSetButExpiresAtIsPresent']</t>
+    <t>['CredentialsManagerException', 'Date', 'shouldNotFailOnGetCredentialsWhenCacheExpiresAtNotSetButExpiresAtIsPresent', 'shouldGetNonExpiredCredentialsFromStorage']</t>
   </si>
   <si>
     <t>[96, 97, 98, 119, 238, 239, 240, 241, 242, 243, 244, 245, 246, 247, 248, 249, 250, 251, 252, 253, 254, 255, 256]</t>
@@ -2207,10 +2059,10 @@
     <t>['auth0/src/main/java/com/auth0/android/provider/AuthenticationActivity.java', 'auth0/src/test/java/com/auth0/android/provider/WebAuthProviderTest.java', 'auth0/src/test/java/com/auth0/android/provider/AuthenticationActivityTest.java']</t>
   </si>
   <si>
-    <t>['AuthenticationActivityTest', 'AuthenticationActivity', 'WebAuthProviderTest']</t>
-  </si>
-  <si>
-    <t>['authenticateUsingWebView', 'authenticateUsingBrowser', 'Intent', 'launchAuthenticationIntent']</t>
+    <t>['AuthenticationActivityTest', 'WebAuthProviderTest', 'AuthenticationActivity']</t>
+  </si>
+  <si>
+    <t>['Intent', 'launchAuthenticationIntent', 'authenticateUsingBrowser', 'authenticateUsingWebView']</t>
   </si>
   <si>
     <t>[17, 25, 33, 81, 96, 26, 255, 273, 276, 293, 296, 142, 157, 173, 188, 203, 217, 230, 244, 259, 274, 288, 301, 316, 331, 346, 360, 373, 388, 403, 418, 432, 445, 460, 473, 488, 503, 517, 530, 545, 558, 571, 585, 599, 613, 629, 645, 660, 674, 712, 724, 736, 750, 763, 776, 789, 802, 815, 828, 841, 857, 870, 890, 907, 924, 941, 964, 967, 989, 992, 1017, 1020, 1056, 1076, 1131, 1170, 1198, 1225, 1252]</t>
@@ -2257,7 +2109,7 @@
     <t>['SecureCredentialsManager', 'SecureCredentialsManagerTest']</t>
   </si>
   <si>
-    <t>['shouldNotHaveCredentialsWhenTheAliasUsedHasNotBeenSetYet', 'shouldNotHaveCredentialsWhenAccessTokenAndIdTokenAreMissing', 'continueGetCredentials', 'CredentialsManagerException', 'shouldNotHaveCredentialsWhenTheAliasUsedHasNotBeenMigratedYet']</t>
+    <t>['shouldNotHaveCredentialsWhenTheAliasUsedHasNotBeenMigratedYet', 'continueGetCredentials', 'shouldNotHaveCredentialsWhenTheAliasUsedHasNotBeenSetYet', 'CredentialsManagerException', 'shouldNotHaveCredentialsWhenAccessTokenAndIdTokenAreMissing']</t>
   </si>
   <si>
     <t>[44, 45, 46, 170, 217, 230, 231, 232, 233, 131, 159, 188, 216, 580, 594, 607, 620, 630, 635, 636, 637, 638, 639, 640, 641, 642, 643, 644, 645, 646, 647, 648, 649, 650, 651, 652, 653, 654, 655, 656, 657, 658, 659, 660, 898]</t>
@@ -2412,7 +2264,7 @@
     <t>['AblyMethodCallHandler']</t>
   </si>
   <si>
-    <t>['ErrorInfo', 'error', 'success', 'Handler', 'CountDownLatch', 'createRealtimeWithOptions']</t>
+    <t>['ErrorInfo', 'success', 'Handler', 'createRealtimeWithOptions', 'error', 'CountDownLatch']</t>
   </si>
   <si>
     <t>[14, 187, 188, 195, 201, 202, 203, 204, 214, 215, 216, 217, 218, 219, 220, 447, 455, 456, 458, 464, 471, 472, 473, 474, 483, 484, 485, 486, 487, 488, 489, 490]</t>
@@ -2464,10 +2316,10 @@
     <t>['android/src/main/java/io/ably/flutter/plugin/AblyMethodCallHandler.java', 'android/src/main/java/io/ably/flutter/plugin/AblyInstanceStore.java']</t>
   </si>
   <si>
-    <t>['AblyMethodCallHandler', 'ReservedClientHandle', 'ClientHandle', 'AblyInstanceStore']</t>
-  </si>
-  <si>
-    <t>['ReservedClientHandle', 'AblyRealtime', 'Handler', 'reserveClientHandle', 'getPushChannel', 'IllegalStateException', 'createRealtime', 'getHandle', 'reset', 'use', 'getRest', 'getPaginatedResult', 'getPush', 'setPaginatedResult', 'getInstance', 'success', 'AblyInstanceStore', 'createRest', 'AblyRest', 'getAblyClient', 'CountDownLatch', 'getRealtime', 'AtomicLong']</t>
+    <t>['AblyInstanceStore', 'ClientHandle', 'AblyMethodCallHandler', 'ReservedClientHandle']</t>
+  </si>
+  <si>
+    <t>['getRest', 'getRealtime', 'createRealtime', 'getAblyClient', 'getInstance', 'ReservedClientHandle', 'success', 'Handler', 'reset', 'AtomicLong', 'AblyInstanceStore', 'reserveClientHandle', 'getPushChannel', 'createRest', 'AblyRest', 'AblyRealtime', 'getHandle', 'use', 'setPaginatedResult', 'getPaginatedResult', 'IllegalStateException', 'getPush', 'CountDownLatch']</t>
   </si>
   <si>
     <t>[6, 7, 37, 44, 45, 46, 47, 49, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79, 82, 83, 84, 85, 86, 87, 88, 89, 90, 91, 92, 93, 94, 95, 96, 97, 98, 99, 100, 101, 102, 103, 104, 105, 106, 107, 108, 109, 110, 111, 112, 113, 114, 115, 116, 117, 118, 119, 122, 123, 126, 127, 130, 144, 149, 154, 160, 163, 171, 175, 186, 192, 223, 451, 457, 490]</t>
@@ -2539,6 +2391,474 @@
   </si>
   <si>
     <t>f9534e5ef650d32dfd330eec35595ce071dca3b0</t>
+  </si>
+  <si>
+    <t>tootallnate/java-websocket</t>
+  </si>
+  <si>
+    <t>https://github.com/tootallnate/java-websocket</t>
+  </si>
+  <si>
+    <t>Continuous binary getting swallowed?</t>
+  </si>
+  <si>
+    <t>My WS JS hosted in Chrome seems to be sending the following frames:_x000D_
+BINARY, isFin = false_x000D_
+CONTINUOUS, isFin = true_x000D_
+_x000D_
+Java-WebSocket seems to drop the CONTINUOUS frame on the floor and the application never gets it:_x000D_
+_x000D_
+```java_x000D_
+// org/java_websocket/drafts/Draft_6455.java:542_x000D_
+} else if( frame.isFin() ) {_x000D_
+	if( current_continuous_frame == null )_x000D_
+		throw new InvalidDataException( CloseFrame.PROTOCOL_ERROR, "Continuous frame sequence was not started." );_x000D_
+	//Check if the whole payload is valid utf8, when the opcode indicates a text_x000D_
+	if( current_continuous_frame.getOpcode() == Framedata.Opcode.TEXT ) {_x000D_
+		//Checking a bit more from the frame before this one just to make sure all the code points are correct_x000D_
+		int off = Math.max( current_continuous_frame.getPayloadData().limit() - 64, 0 );_x000D_
+		current_continuous_frame.append( frame );_x000D_
+		if( !Charsetfunctions.isValidUTF8( current_continuous_frame.getPayloadData(), off ) ) {_x000D_
+			throw new InvalidDataException( CloseFrame.NO_UTF8 );_x000D_
+		}_x000D_
+	}_x000D_
+	// **** What about if the current_continuous_frame.getOpcode() == Framedata.Opcode.BINARY ****//_x000D_
+	current_continuous_frame = null;_x000D_
+```_x000D_
+_x000D_
+Is this expected? Is Chrome breaking the spec? Is this something Java-WebSocket should handle differently?</t>
+  </si>
+  <si>
+    <t>https://github.com/TooTallNate/Java-WebSocket/issues/564</t>
+  </si>
+  <si>
+    <t>['src/main/java/org/java_websocket/drafts/Draft_6455.java', 'src/main/java/org/java_websocket/WebSocketImpl.java', 'src/test/java/org/java_websocket/example/AutobahnServerTest.java', 'src/main/java/org/java_websocket/server/WebSocketServer.java', 'src/main/java/org/java_websocket/WebSocketListener.java']</t>
+  </si>
+  <si>
+    <t>['WebSocketImpl', 'WebSocketServer', 'WebSocketListener', 'Draft_6455', 'AutobahnServerTest']</t>
+  </si>
+  <si>
+    <t>['getRemoteSocketAddress', 'getFlashPolicy', 'main', 'onWebsocketHandshakeSentAsClient', 'InvalidDataException', 'onWebsocketOpen', 'IllegalArgumentException', 'onMessage', 'onWebsocketCloseInitiated', 'InetSocketAddress', 'getPayloadFromByteBufferList', 'if', 'onWriteDemand', 'WebsocketNotConnectedException', 'LimitExedeedException', 'onWebsocketHandshakeReceivedAsClient', 'onWebsocketClose', 'onWebsocketClosing', 'onWebsocketError', 'onWebsocketMessageFragment', 'onWebsocketMessage', 'getLocalSocketAddress', 'onWebsocketPong', 'onFragment', 'Draft_6455', 'hashCode', 'onWebsocketPing', 'AutobahnServerTest', 'onWebsocketHandshakeReceivedAsServer']</t>
+  </si>
+  <si>
+    <t>[608, 62, 77, 90, 101, 112, 117, 122, 123, 133, 144, 153, 161, 172, 181, 189, 197, 198, 203, 211, 219, 65, 66, 67, 68, 69, 104, 557, 561, 563, 564, 565, 566, 567, 568, 569, 570, 571, 572, 573, 574, 575, 576, 580, 591, 592, 642, 643, 644, 645, 646, 647, 648, 649, 650, 651, 652, 653, 654, 655, 656, 657, 658, 659, 660, 661, 662, 770, 86, 87, 91, 92]</t>
+  </si>
+  <si>
+    <t>https://github.com/tootallnate/java-websocket/compare/f33422e9951369ffd948d473c026ef0e6da6b8e4...32c1ce01c9064d68c8adcfa3b1b577d30bed8cb2</t>
+  </si>
+  <si>
+    <t>f33422e9951369ffd948d473c026ef0e6da6b8e4</t>
+  </si>
+  <si>
+    <t>32c1ce01c9064d68c8adcfa3b1b577d30bed8cb2</t>
+  </si>
+  <si>
+    <t>WebSocketServer freezes in stop() method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hello,
+first I would like to thank you for creating a great and useful library.
+I'am using it in Android application to communicate with website. 
+When I try to stop the server, the application sometimes stops responding.
+The main thread is indefinitely waiting in "WebSocketServer.stop()" method in "selectorThread.join()" line, because the "selectorThread" never ends. This happens because "selectorThread" is waiting in "run()" method in "selector.select()" line.
+Do you know what could be the cause of this behavior?
+Thank you all in advance for any help you can provide.
+Regards,
+Vito
+</t>
+  </si>
+  <si>
+    <t>https://github.com/TooTallNate/Java-WebSocket/issues/259</t>
+  </si>
+  <si>
+    <t>['src/main/java/org/java_websocket/server/WebSocketServer.java']</t>
+  </si>
+  <si>
+    <t>['WebSocketServer']</t>
+  </si>
+  <si>
+    <t>[219, 220, 221, 222]</t>
+  </si>
+  <si>
+    <t>https://github.com/tootallnate/java-websocket/compare/ac45d846806ad662de48c206896d1248acbb53ff...e4c248a69f0cb36f87e5b3d3100bd2b46e027289</t>
+  </si>
+  <si>
+    <t>ac45d846806ad662de48c206896d1248acbb53ff</t>
+  </si>
+  <si>
+    <t>e4c248a69f0cb36f87e5b3d3100bd2b46e027289</t>
+  </si>
+  <si>
+    <t>Bad rsv 4 on android</t>
+  </si>
+  <si>
+    <t>Hello, our team using this library for connecting websocket server on Android platform,_x000D_
+sometimes,  there are 'bad rsv 4' errors occurred. Seems same problem with #430._x000D_
+_x000D_
+```_x000D_
+04-27 14:26:09.960 I/System.out( 1564): D/WebsocketChannel: 000000	48 54 54 50 2f 31 2e 31 20 31 30 31 20 53 77 69 74 63  HTTP/1.1 101 Switc_x000D_
+04-27 14:26:09.960 D/WebSocketChannel( 1564): onError:org.java_websocket.exceptions.InvalidFrameException: bad rsv 4_x000D_
+```_x000D_
+_x000D_
+The debug log above shows the **WebSocketImpl** treat the handshake response as normal websocket frame and decode it, then throw an InvalidFrameException._x000D_
+_x000D_
+Our client tries to reconnect to server endlessly when it is in condition of unstable network environment. _x000D_
+So is it possible that method **org.java_websocket.WebSocketImpl#decode**  was invoked after **WebSocketClient** closed in some extreme cases?</t>
+  </si>
+  <si>
+    <t>https://github.com/TooTallNate/Java-WebSocket/issues/465</t>
+  </si>
+  <si>
+    <t>['src/main/java/org/java_websocket/WebSocketImpl.java']</t>
+  </si>
+  <si>
+    <t>['WebSocketImpl']</t>
+  </si>
+  <si>
+    <t>['String']</t>
+  </si>
+  <si>
+    <t>[154, 155, 156]</t>
+  </si>
+  <si>
+    <t>https://github.com/tootallnate/java-websocket/compare/b983c881b2dfb9f4c607f4b8b8201666e3491a12...2daee16dacbf1e0a9186f260310400a03c10803d</t>
+  </si>
+  <si>
+    <t>b983c881b2dfb9f4c607f4b8b8201666e3491a12</t>
+  </si>
+  <si>
+    <t>2daee16dacbf1e0a9186f260310400a03c10803d</t>
+  </si>
+  <si>
+    <t>Endless loop in client upon close() when using wss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First, thanks so much for creating the library, it's really useful. I am using this via gottox/socket-io (client) and have run into this nasty problem of an endless loop in SSLSocketChannel2.java when closing a connection (maybe after the other side closed first). A couple of these failures is all it takes to pin the CPU at 100% as the threads that execute these loops pile up.
+I doubt this is the correct fix, but what I did was change the following in SSLSocketChannel2.readRemaining(), which seems to work.
+``` java
+        if( inCrypt.hasRemaining() ) {
+            unwrap();
+            int amount = transfereTo( inData, dst );
+&gt;&gt;&gt;         if (engineStatus == SSLEngineResult.Status.CLOSED) {
+&gt;&gt;&gt;             return -1;
+&gt;&gt;&gt;         }
+            if( amount &gt; 0 )
+                return amount;
+        }
+```
+EDIT by @Davidisudadi: formatted code
+</t>
+  </si>
+  <si>
+    <t>https://github.com/TooTallNate/Java-WebSocket/issues/171</t>
+  </si>
+  <si>
+    <t>['src/main/java/org/java_websocket/SSLSocketChannel2.java']</t>
+  </si>
+  <si>
+    <t>['SSLSocketChannel2']</t>
+  </si>
+  <si>
+    <t>['EOFException']</t>
+  </si>
+  <si>
+    <t>[8, 9, 10, 11, 12, 13, 14, 216, 217, 218, 292, 293, 294]</t>
+  </si>
+  <si>
+    <t>https://github.com/tootallnate/java-websocket/compare/05d2e2ed045d955947d944d7111ce3e6758843b6...ea7e061369477bfdf5a0c32bad920c91f8af61fb</t>
+  </si>
+  <si>
+    <t>05d2e2ed045d955947d944d7111ce3e6758843b6</t>
+  </si>
+  <si>
+    <t>ea7e061369477bfdf5a0c32bad920c91f8af61fb</t>
+  </si>
+  <si>
+    <t>Websocket server returning 401; can't handle on client side</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I have a websocket server that returns 401 on the http handshake
+I can't figure out how to get that information on the websocket client
+Two things I can't figure out:
+1. Where can I get the http status code returned form the server (401 in this case)
+   onClose is called but with irrelevant code (-1) which I saw in your code that it means "never connected"
+2. onError is called but for totally different reason. I get onError ssl == null
+   why would the client library continue to try to decode the handshake, or something like that, when the socket wasn't upgraded (101)? why not just stop there? The ssl error is irrelevant here and is fired do to the fact that the server did not upgrade the socket
+What I did to get the status code from the server was to subclass my own Draft, implement acceptHandshakeAsClient and copyInsance; this gave me access to the handshake response
+When I see that the status code is 401 I return NOT_MATCHED
+This is the only place I saw I can get the status code, but it makes me do ugly things like saving the status code in a variable to be used by onClose and onError which are then called (but with irrelevant data - code == -1 and error exception is ssl == null)
+Thanks
+</t>
+  </si>
+  <si>
+    <t>https://github.com/TooTallNate/Java-WebSocket/issues/390</t>
+  </si>
+  <si>
+    <t>['if']</t>
+  </si>
+  <si>
+    <t>[450, 451]</t>
+  </si>
+  <si>
+    <t>https://github.com/tootallnate/java-websocket/compare/37b4610cd6c5b5f717b8c4ca196947019a0ed8b1...f1eeff4c3b677a503d04d260475b9725445a82d6</t>
+  </si>
+  <si>
+    <t>37b4610cd6c5b5f717b8c4ca196947019a0ed8b1</t>
+  </si>
+  <si>
+    <t>f1eeff4c3b677a503d04d260475b9725445a82d6</t>
+  </si>
+  <si>
+    <t>Broken prefix list page web UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check out nipap-demo.spritelink.net - I'm just getting a big ugly error message: "undefined".
+I ran nipapd with -d -f and it appears to work OK.
+Could this be that the web-UI expects the interpretation result to look differently? 
+</t>
+  </si>
+  <si>
+    <t>https://github.com/SpriteLink/NIPAP/issues/1004</t>
+  </si>
+  <si>
+    <t>['nipap-www/nipapwww/controllers/xhr.py']</t>
+  </si>
+  <si>
+    <t>['XhrController']</t>
+  </si>
+  <si>
+    <t>[112, 113, 114, 115, 116, 117, 242, 243, 244, 245, 246, 247, 511, 512, 513, 514, 515, 516]</t>
+  </si>
+  <si>
+    <t>https://github.com/spritelink/nipap/compare/df9ac80c238d3d052b661237a993df8b27d3eb12...59404e82d5756e7b4a6261cec0eaf7ead9f5e30c</t>
+  </si>
+  <si>
+    <t>df9ac80c238d3d052b661237a993df8b27d3eb12</t>
+  </si>
+  <si>
+    <t>59404e82d5756e7b4a6261cec0eaf7ead9f5e30c</t>
+  </si>
+  <si>
+    <t>SCLOPF returns TypeError with pyomo=False unless run with pyomo=True first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">## Checklist_x000D_
+_x000D_
+- [x] I am using the current [`master`](https://github.com/pypsa/pypsa/tree/master) branch or the latest [release](https://github.com/pypsa/pypsa/releases). Please indicate:_x000D_
+_x000D_
+## Describe the Bug_x000D_
+_x000D_
+Running `sclopf` with `pyomo=False` returns a concatenation-related `TypeError`. However, running `sclopf` with `pyomo=True` on the same network and then running with `pyomo=False` again works. This explains why the unit test (which runs in a loop with True first then False) does not fail. First observed this on my own case then reproduced using the unit test case._x000D_
+_x000D_
+## (MWE and) Error Message_x000D_
+MWE (repurposed from `test_sclopf_scigrid.py`):_x000D_
+_x000D_
+```python_x000D_
+In [1]: import pypsa_x000D_
+_x000D_
+In [2]: n = pypsa.Network("../../PyPSA/examples/scigrid-de/scigrid-with-load-gen-trafos/")_x000D_
+WARNING:pypsa.io:_x000D_
+Importing PyPSA from older version of PyPSA than current version._x000D_
+Please read the release notes at https://pypsa.readthedocs.io/en/latest/release_notes.html_x000D_
+carefully to prepare your network for import._x000D_
+Currently used PyPSA version [0, 20, 0], imported network file PyPSA version [0, 10, 0]._x000D_
+_x000D_
+INFO:pypsa.components:Applying weightings to all columns of `snapshot_weightings`_x000D_
+INFO:pypsa.io:Imported network nan has buses, generators, lines, loads, storage_units, transformers_x000D_
+_x000D_
+In [3]: for line_name in ["316", "527", "602"]:_x000D_
+   ...:     n.lines.loc[line_name, "s_nom"] = 1200_x000D_
+   ...: branch_outages = n.lines.index[:2]_x000D_
+_x000D_
+In [4]: n.sclopf(_x000D_
+   ...:     n.snapshots[0],_x000D_
+   ...:     branch_outages=branch_outages,_x000D_
+   ...:     pyomo=False,  # running with pyomo=False first_x000D_
+   ...:     solver_name="cbc",_x000D_
+   ...: )_x000D_
+INFO:pypsa.linopf:Prepare linear problem_x000D_
+---------------------------------------------------------------------------_x000D_
+TypeError                                 Traceback (most recent call last)_x000D_
+Input In [4], in &lt;cell line: 1&gt;()_x000D_
+----&gt; 1 n.sclopf(_x000D_
+      2     n.snapshots[0],_x000D_
+      3     branch_outages=branch_outages,_x000D_
+      4     pyomo=False,_x000D_
+      5     solver_name="cbc",_x000D_
+      6 )_x000D_
+_x000D_
+File ~/PyPSA/pypsa/contingency.py:464, in network_sclopf(network, snapshots, branch_outages, solver_name, pyomo, skip_pre, extra_functionality, solver_options, keep_files, formulation, ptdf_tolerance)_x000D_
+    460     pyomo_kwargs["ptdf_tolerance"] = ptdf_tolerance_x000D_
+    462 # need to skip preparation otherwise it recalculates the sub-networks_x000D_
+--&gt; 464 network.lopf(_x000D_
+    465     snapshots=snapshots,_x000D_
+    466     solver_name=solver_name,_x000D_
+    467     pyomo=pyomo,_x000D_
+    468     skip_pre=True,_x000D_
+    469     extra_functionality=_extra_functionality,_x000D_
+    470     solver_options=solver_options,_x000D_
+    471     keep_files=keep_files,_x000D_
+    472     formulation=formulation,_x000D_
+    473     **pyomo_kwargs,_x000D_
+    474 )_x000D_
+_x000D_
+File ~/PyPSA/pypsa/components.py:752, in Network.lopf(self, snapshots, pyomo, solver_name, solver_options, solver_logfile, formulation, keep_files, extra_functionality, multi_investment_periods, **kwargs)_x000D_
+    750     return network_lopf(self, **args)_x000D_
+    751 else:_x000D_
+--&gt; 752     return network_lopf_lowmem(self, **args)_x000D_
+_x000D_
+File ~/PyPSA/pypsa/linopf.py:1450, in network_lopf(n, snapshots, solver_name, solver_logfile, extra_functionality, multi_investment_periods, skip_objective, skip_pre, extra_postprocessing, formulation, keep_references, keep_files, keep_shadowprices, solver_options, warmstart, store_basis, solver_dir)_x000D_
+   1447     n.determine_network_topology()_x000D_
+   1449 logger.info("Prepare linear problem")_x000D_
+-&gt; 1450 fdp, problem_fn = prepare_lopf(_x000D_
+   1451     n, snapshots, keep_files, skip_objective, extra_functionality, solver_dir_x000D_
+   1452 )_x000D_
+   1453 fds, solution_fn = mkstemp(prefix="pypsa-solve", suffix=".sol", dir=solver_dir)_x000D_
+   1455 if warmstart == True:_x000D_
+_x000D_
+File ~/PyPSA/pypsa/linopf.py:1107, in prepare_lopf(n, snapshots, keep_files, skip_objective, extra_functionality, solver_dir)_x000D_
+   1105 define_storage_unit_constraints(n, snapshots)_x000D_
+   1106 define_store_constraints(n, snapshots)_x000D_
+-&gt; 1107 define_kirchhoff_constraints(n, snapshots)_x000D_
+   1108 define_nodal_balance_constraints(n, snapshots)_x000D_
+   1109 define_global_constraints(n, snapshots)_x000D_
+_x000D_
+File ~/PyPSA/pypsa/linopf.py:508, in define_kirchhoff_constraints(n, sns)_x000D_
+    505     snapshots = sns if period == None else sns[sns.get_loc(period)]_x000D_
+    506     cycle_sum.set_index(snapshots, inplace=True)_x000D_
+--&gt; 508     con = write_constraint(n, cycle_sum, "=", 0)_x000D_
+    509     subconstraints.append(con)_x000D_
+    510 if len(subconstraints) == 0:_x000D_
+_x000D_
+File ~/PyPSA/pypsa/linopt.py:270, in write_constraint(n, lhs, sense, rhs, axes, mask)_x000D_
+    268     sense = "=" if sense == "==" else sense_x000D_
+    269 lhs, sense, rhs = _str_array(lhs), _str_array(sense), _str_array(rhs)_x000D_
+--&gt; 270 exprs = "c" + _str_array(cons, True) + ":\\n" + lhs + sense + " " + rhs + "\\n\\n"_x000D_
+    271 if mask is not None:_x000D_
+    272     exprs = np.where(mask, exprs, "")_x000D_
+_x000D_
+TypeError: can only concatenate str (not "int") to str_x000D_
+_x000D_
+In [5]: n.sclopf(_x000D_
+   ...:     n.snapshots[0],_x000D_
+   ...:     branch_outages=branch_outages,_x000D_
+   ...:     pyomo=True,  # running with pyomo=True works_x000D_
+   ...:     solver_name="cbc",_x000D_
+   ...: )_x000D_
+WARNING:pypsa.components:Solving optimisation problem with pyomo.In PyPSA version 0.21 the default will change to ``n.lopf(pyomo=False)``.Explicitly set ``n.lopf(pyomo=True)`` to retain current behaviour._x000D_
+INFO:pypsa.opf:Building pyomo model using `kirchhoff` formulation_x000D_
+WARNING:pypsa.contingency:No type given for 1, assuming it is a line_x000D_
+WARNING:pypsa.contingency:No type given for 2, assuming it is a line_x000D_
+INFO:pypsa.opf:Solving model using cbc_x000D_
+# ==========================================================_x000D_
+# = Solver Results                                         =_x000D_
+# ==========================================================_x000D_
+# ----------------------------------------------------------_x000D_
+#   Problem Information_x000D_
+# ----------------------------------------------------------_x000D_
+Problem: _x000D_
+- Name: unknown_x000D_
+  Lower bound: 339758.4578_x000D_
+  Upper bound: 339758.4578_x000D_
+  Number of objectives: 1_x000D_
+  Number of constraints: 6714_x000D_
+  Number of variables: 2486_x000D_
+  Number of nonzeros: 438_x000D_
+  Sense: minimize_x000D_
+# ----------------------------------------------------------_x000D_
+#   Solver Information_x000D_
+# ----------------------------------------------------------_x000D_
+Solver: _x000D_
+- Status: ok_x000D_
+  User time: -1.0_x000D_
+  System time: 0.13_x000D_
+  Wallclock time: 0.14_x000D_
+  Termination condition: optimal_x000D_
+  Termination message: Model was solved to optimality (subject to tolerances), and an optimal solution is available._x000D_
+  Statistics: _x000D_
+    Branch and bound: _x000D_
+      Number of bounded subproblems: None_x000D_
+      Number of created subproblems: None_x000D_
+    Black box: _x000D_
+      Number of iterations: 760_x000D_
+  Error rc: 0_x000D_
+  Time: 0.15059161186218262_x000D_
+# ----------------------------------------------------------_x000D_
+#   Solution Information_x000D_
+# ----------------------------------------------------------_x000D_
+Solution: _x000D_
+- number of solutions: 0_x000D_
+  number of solutions displayed: 0_x000D_
+INFO:pypsa.opf:Optimization successful_x000D_
+_x000D_
+In [6]: n.sclopf(_x000D_
+   ...:     n.snapshots[0],_x000D_
+   ...:     branch_outages=branch_outages,_x000D_
+   ...:     pyomo=False,  # after successfully running with pyomo=True, running again with False (same as In[4]) works fine._x000D_
+   ...:     solver_name="cbc",_x000D_
+   ...: )_x000D_
+INFO:pypsa.linopf:Prepare linear problem_x000D_
+INFO:pypsa.linopf:Total preparation time: 4.23s_x000D_
+INFO:pypsa.linopf:Solve linear problem using Cbc solver_x000D_
+INFO:pypsa.linopf:Optimization successful. Objective value: 3.40e+05_x000D_
+```_x000D_
+</t>
+  </si>
+  <si>
+    <t>https://github.com/PyPSA/PyPSA/issues/436</t>
+  </si>
+  <si>
+    <t>['test/conftest.py', 'test/test_sclopf_scigrid.py', 'pypsa/contingency.py']</t>
+  </si>
+  <si>
+    <t>['test_sclopf', 'test_sclopf_pyomo', 'scipy_network', 'network_sclopf']</t>
+  </si>
+  <si>
+    <t>[436, 18, 4, 11, 12, 22, 23, 24, 25, 26, 27, 29, 30, 31, 33, 35, 37, 39, 40, 41, 43, 45]</t>
+  </si>
+  <si>
+    <t>https://github.com/pypsa/pypsa/compare/9eeffb18ebeeae0448d36579c52738496ee7388b...632d62528c6118058c13d7e68b414d18bb6708c6</t>
+  </si>
+  <si>
+    <t>9eeffb18ebeeae0448d36579c52738496ee7388b</t>
+  </si>
+  <si>
+    <t>632d62528c6118058c13d7e68b414d18bb6708c6</t>
+  </si>
+  <si>
+    <t>Template for test yaml is incorrect when using "contains"</t>
+  </si>
+  <si>
+    <t>### Description of the bug
+"contains" in `test_yml_builder.py` in both `subworklows` and `modules` is currently outputting a string in the yml but it needs to be an array of strings._x000D_
+_x000D_
+See https://github.com/nf-core/modules/pull/2204_x000D_
+_x000D_
+### Command used and terminal output
+_No response_
+### System information
+Tools version 2.7</t>
+  </si>
+  <si>
+    <t>https://github.com/nf-core/tools/issues/1922</t>
+  </si>
+  <si>
+    <t>['nf_core/subworkflows/test_yml_builder.py', 'nf_core/modules/test_yml_builder.py', 'nf_core/modules/modules_repo.py']</t>
+  </si>
+  <si>
+    <t>['SubworkflowTestYmlBuilder', 'ModulesRepo', 'ModulesTestYmlBuilder']</t>
+  </si>
+  <si>
+    <t>[384, 385, 386, 387, 290, 291, 292, 308, 309, 310]</t>
+  </si>
+  <si>
+    <t>https://github.com/nf-core/tools/compare/be8978bad527172c4a32b4888e8abfe5fe5954d8...940a7bd5fd7b56ea45db40c09332181720683cb5</t>
+  </si>
+  <si>
+    <t>be8978bad527172c4a32b4888e8abfe5fe5954d8</t>
+  </si>
+  <si>
+    <t>940a7bd5fd7b56ea45db40c09332181720683cb5</t>
   </si>
 </sst>
 </file>
@@ -2901,10 +3221,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="38.109375" customWidth="1"/>
+    <col min="2" max="2" width="40.109375" customWidth="1"/>
+    <col min="6" max="6" width="28.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -3194,46 +3515,46 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="D7">
-        <v>170</v>
+        <v>447</v>
       </c>
       <c r="E7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="H7" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="I7" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="J7" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="K7" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="L7" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="M7" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="N7" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="O7" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
@@ -3241,46 +3562,46 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="D8">
-        <v>170</v>
+        <v>447</v>
       </c>
       <c r="E8">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="I8" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="J8" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="K8" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="L8" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="M8" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="N8" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="O8" t="s">
-        <v>37</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
@@ -3288,46 +3609,46 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="D9">
-        <v>170</v>
+        <v>447</v>
       </c>
       <c r="E9">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="H9" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="I9" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="J9" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="K9" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="L9" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="M9" t="s">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="N9" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="O9" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
@@ -3335,46 +3656,46 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="D10">
-        <v>170</v>
+        <v>447</v>
       </c>
       <c r="E10">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="G10" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="H10" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="I10" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="J10" t="s">
         <v>51</v>
       </c>
       <c r="K10" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="L10" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="M10" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="N10" t="s">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="O10" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
@@ -3382,46 +3703,46 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="D11">
-        <v>170</v>
+        <v>447</v>
       </c>
       <c r="E11">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>492</v>
       </c>
       <c r="G11" t="s">
-        <v>58</v>
+        <v>493</v>
       </c>
       <c r="H11" t="s">
-        <v>59</v>
+        <v>494</v>
       </c>
       <c r="I11" t="s">
-        <v>60</v>
+        <v>495</v>
       </c>
       <c r="J11" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K11" t="s">
-        <v>61</v>
+        <v>496</v>
       </c>
       <c r="L11" t="s">
-        <v>62</v>
+        <v>497</v>
       </c>
       <c r="M11" t="s">
-        <v>63</v>
+        <v>498</v>
       </c>
       <c r="N11" t="s">
-        <v>64</v>
+        <v>499</v>
       </c>
       <c r="O11" t="s">
-        <v>65</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
@@ -3441,34 +3762,34 @@
         <v>55</v>
       </c>
       <c r="F12" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="G12" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="H12" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="I12" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="J12" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="K12" t="s">
-        <v>51</v>
+        <v>108</v>
       </c>
       <c r="L12" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="M12" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="N12" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="O12" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
@@ -3476,46 +3797,46 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="D13">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="E13">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="H13" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="I13" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="J13" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="K13" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="L13" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="M13" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="N13" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="O13" t="s">
-        <v>85</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
@@ -3523,46 +3844,46 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="D14">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="E14">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F14" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="G14" t="s">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="H14" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="I14" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="J14" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="K14" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="L14" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="M14" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="N14" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="O14" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
@@ -3570,46 +3891,46 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="D15">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="E15">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F15" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="G15" t="s">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="H15" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="I15" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="J15" t="s">
+        <v>138</v>
+      </c>
+      <c r="K15" t="s">
         <v>51</v>
       </c>
-      <c r="K15" t="s">
-        <v>100</v>
-      </c>
       <c r="L15" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="M15" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="O15" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -3617,46 +3938,46 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="D16">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="E16">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F16" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="G16" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="H16" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="I16" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="J16" t="s">
+        <v>147</v>
+      </c>
+      <c r="K16" t="s">
         <v>51</v>
       </c>
-      <c r="K16" t="s">
-        <v>108</v>
-      </c>
       <c r="L16" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="M16" t="s">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="N16" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="O16" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
@@ -3664,46 +3985,46 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="D17">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="E17">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F17" t="s">
-        <v>113</v>
+        <v>483</v>
       </c>
       <c r="G17" t="s">
-        <v>114</v>
+        <v>484</v>
       </c>
       <c r="H17" t="s">
-        <v>115</v>
+        <v>485</v>
       </c>
       <c r="I17" t="s">
-        <v>116</v>
+        <v>486</v>
       </c>
       <c r="J17" t="s">
+        <v>487</v>
+      </c>
+      <c r="K17" t="s">
         <v>51</v>
       </c>
-      <c r="K17" t="s">
-        <v>117</v>
-      </c>
       <c r="L17" t="s">
-        <v>118</v>
+        <v>488</v>
       </c>
       <c r="M17" t="s">
-        <v>119</v>
+        <v>489</v>
       </c>
       <c r="N17" t="s">
-        <v>120</v>
+        <v>490</v>
       </c>
       <c r="O17" t="s">
-        <v>121</v>
+        <v>491</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
@@ -3711,46 +4032,46 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="D18">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="E18">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F18" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="G18" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="H18" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="I18" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J18" t="s">
         <v>51</v>
       </c>
       <c r="K18" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="L18" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="M18" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="N18" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="O18" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
@@ -3758,46 +4079,46 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>161</v>
       </c>
       <c r="D19">
-        <v>447</v>
+        <v>249</v>
       </c>
       <c r="E19">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="G19" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="H19" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="I19" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="J19" t="s">
+        <v>166</v>
+      </c>
+      <c r="K19" t="s">
         <v>51</v>
       </c>
-      <c r="K19" t="s">
-        <v>135</v>
-      </c>
       <c r="L19" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="M19" t="s">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="N19" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="O19" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
@@ -3805,46 +4126,46 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>161</v>
       </c>
       <c r="D20">
-        <v>447</v>
+        <v>249</v>
       </c>
       <c r="E20">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F20" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="G20" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="H20" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="I20" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="J20" t="s">
         <v>51</v>
       </c>
       <c r="K20" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="L20" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="M20" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="N20" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="O20" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
@@ -3852,46 +4173,46 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>161</v>
       </c>
       <c r="D21">
-        <v>447</v>
+        <v>249</v>
       </c>
       <c r="E21">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F21" t="s">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="G21" t="s">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="H21" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="I21" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="J21" t="s">
-        <v>51</v>
+        <v>184</v>
       </c>
       <c r="K21" t="s">
-        <v>51</v>
+        <v>185</v>
       </c>
       <c r="L21" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="M21" t="s">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="N21" t="s">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="O21" t="s">
-        <v>156</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
@@ -3899,46 +4220,46 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C22" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D22">
-        <v>360</v>
+        <v>249</v>
       </c>
       <c r="E22">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F22" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="G22" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="H22" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="I22" t="s">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="J22" t="s">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="K22" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="L22" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="M22" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="N22" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="O22" t="s">
-        <v>168</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
@@ -3946,46 +4267,46 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C23" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D23">
-        <v>360</v>
+        <v>249</v>
       </c>
       <c r="E23">
+        <v>56</v>
+      </c>
+      <c r="F23" t="s">
+        <v>501</v>
+      </c>
+      <c r="G23" t="s">
+        <v>502</v>
+      </c>
+      <c r="H23" t="s">
+        <v>503</v>
+      </c>
+      <c r="I23" t="s">
+        <v>504</v>
+      </c>
+      <c r="J23" t="s">
+        <v>505</v>
+      </c>
+      <c r="K23" t="s">
         <v>51</v>
       </c>
-      <c r="F23" t="s">
-        <v>169</v>
-      </c>
-      <c r="G23" t="s">
-        <v>170</v>
-      </c>
-      <c r="H23" t="s">
-        <v>171</v>
-      </c>
-      <c r="I23" t="s">
-        <v>172</v>
-      </c>
-      <c r="J23" t="s">
-        <v>51</v>
-      </c>
-      <c r="K23" t="s">
-        <v>173</v>
-      </c>
       <c r="L23" t="s">
-        <v>174</v>
+        <v>506</v>
       </c>
       <c r="M23" t="s">
-        <v>175</v>
+        <v>507</v>
       </c>
       <c r="N23" t="s">
-        <v>176</v>
+        <v>508</v>
       </c>
       <c r="O23" t="s">
-        <v>177</v>
+        <v>509</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
@@ -3993,46 +4314,46 @@
         <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C24" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D24">
-        <v>360</v>
+        <v>249</v>
       </c>
       <c r="E24">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F24" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="G24" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="H24" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="I24" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="J24" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="K24" t="s">
         <v>51</v>
       </c>
       <c r="L24" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="M24" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="N24" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="O24" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
@@ -4040,46 +4361,46 @@
         <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>157</v>
+        <v>209</v>
       </c>
       <c r="C25" t="s">
-        <v>158</v>
+        <v>210</v>
       </c>
       <c r="D25">
-        <v>360</v>
+        <v>254</v>
       </c>
       <c r="E25">
+        <v>56</v>
+      </c>
+      <c r="F25" t="s">
+        <v>211</v>
+      </c>
+      <c r="G25" t="s">
+        <v>212</v>
+      </c>
+      <c r="H25" t="s">
+        <v>213</v>
+      </c>
+      <c r="I25" t="s">
+        <v>214</v>
+      </c>
+      <c r="J25" t="s">
         <v>51</v>
       </c>
-      <c r="F25" t="s">
-        <v>187</v>
-      </c>
-      <c r="G25" t="s">
-        <v>188</v>
-      </c>
-      <c r="H25" t="s">
-        <v>189</v>
-      </c>
-      <c r="I25" t="s">
-        <v>190</v>
-      </c>
-      <c r="J25" t="s">
-        <v>191</v>
-      </c>
       <c r="K25" t="s">
-        <v>51</v>
+        <v>215</v>
       </c>
       <c r="L25" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="M25" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="N25" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="O25" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
@@ -4087,46 +4408,46 @@
         <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>157</v>
+        <v>209</v>
       </c>
       <c r="C26" t="s">
-        <v>158</v>
+        <v>210</v>
       </c>
       <c r="D26">
-        <v>360</v>
+        <v>254</v>
       </c>
       <c r="E26">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F26" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="G26" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="H26" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="I26" t="s">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="J26" t="s">
-        <v>51</v>
+        <v>224</v>
       </c>
       <c r="K26" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="L26" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="M26" t="s">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="N26" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="O26" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
@@ -4134,46 +4455,46 @@
         <v>15</v>
       </c>
       <c r="B27" t="s">
-        <v>157</v>
+        <v>209</v>
       </c>
       <c r="C27" t="s">
-        <v>158</v>
+        <v>210</v>
       </c>
       <c r="D27">
-        <v>360</v>
+        <v>254</v>
       </c>
       <c r="E27">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F27" t="s">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="G27" t="s">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="H27" t="s">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="I27" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="J27" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="K27" t="s">
-        <v>51</v>
+        <v>234</v>
       </c>
       <c r="L27" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="M27" t="s">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="N27" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="O27" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
@@ -4181,46 +4502,46 @@
         <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>157</v>
+        <v>209</v>
       </c>
       <c r="C28" t="s">
-        <v>158</v>
+        <v>210</v>
       </c>
       <c r="D28">
-        <v>360</v>
+        <v>254</v>
       </c>
       <c r="E28">
+        <v>56</v>
+      </c>
+      <c r="F28" t="s">
+        <v>239</v>
+      </c>
+      <c r="G28" t="s">
+        <v>240</v>
+      </c>
+      <c r="H28" t="s">
+        <v>241</v>
+      </c>
+      <c r="I28" t="s">
+        <v>242</v>
+      </c>
+      <c r="J28" t="s">
         <v>51</v>
       </c>
-      <c r="F28" t="s">
-        <v>213</v>
-      </c>
-      <c r="G28" t="s">
-        <v>214</v>
-      </c>
-      <c r="H28" t="s">
-        <v>215</v>
-      </c>
-      <c r="I28" t="s">
-        <v>216</v>
-      </c>
-      <c r="J28" t="s">
-        <v>217</v>
-      </c>
       <c r="K28" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="L28" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="M28" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="N28" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="O28" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
@@ -4228,46 +4549,46 @@
         <v>15</v>
       </c>
       <c r="B29" t="s">
-        <v>157</v>
+        <v>248</v>
       </c>
       <c r="C29" t="s">
-        <v>158</v>
+        <v>249</v>
       </c>
       <c r="D29">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="E29">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F29" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="G29" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="H29" t="s">
-        <v>225</v>
+        <v>252</v>
       </c>
       <c r="I29" t="s">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="J29" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="K29" t="s">
-        <v>51</v>
+        <v>255</v>
       </c>
       <c r="L29" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="M29" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="N29" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="O29" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
@@ -4275,46 +4596,46 @@
         <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>157</v>
+        <v>248</v>
       </c>
       <c r="C30" t="s">
-        <v>158</v>
+        <v>249</v>
       </c>
       <c r="D30">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="E30">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F30" t="s">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="G30" t="s">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="H30" t="s">
-        <v>234</v>
+        <v>262</v>
       </c>
       <c r="I30" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="J30" t="s">
-        <v>236</v>
+        <v>264</v>
       </c>
       <c r="K30" t="s">
-        <v>51</v>
+        <v>265</v>
       </c>
       <c r="L30" t="s">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="M30" t="s">
-        <v>238</v>
+        <v>267</v>
       </c>
       <c r="N30" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="O30" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
@@ -4322,46 +4643,46 @@
         <v>15</v>
       </c>
       <c r="B31" t="s">
-        <v>157</v>
+        <v>248</v>
       </c>
       <c r="C31" t="s">
-        <v>158</v>
+        <v>249</v>
       </c>
       <c r="D31">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="E31">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F31" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="G31" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="H31" t="s">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="I31" t="s">
-        <v>181</v>
+        <v>273</v>
       </c>
       <c r="J31" t="s">
-        <v>182</v>
+        <v>274</v>
       </c>
       <c r="K31" t="s">
-        <v>51</v>
+        <v>275</v>
       </c>
       <c r="L31" t="s">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="M31" t="s">
-        <v>245</v>
+        <v>277</v>
       </c>
       <c r="N31" t="s">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="O31" t="s">
-        <v>247</v>
+        <v>279</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
@@ -4375,40 +4696,40 @@
         <v>249</v>
       </c>
       <c r="D32">
-        <v>249</v>
+        <v>341</v>
       </c>
       <c r="E32">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F32" t="s">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="G32" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="H32" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="I32" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="J32" t="s">
-        <v>254</v>
+        <v>51</v>
       </c>
       <c r="K32" t="s">
-        <v>51</v>
+        <v>284</v>
       </c>
       <c r="L32" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="M32" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="N32" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="O32" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
@@ -4422,40 +4743,40 @@
         <v>249</v>
       </c>
       <c r="D33">
-        <v>249</v>
+        <v>341</v>
       </c>
       <c r="E33">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F33" t="s">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="G33" t="s">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="H33" t="s">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="I33" t="s">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="J33" t="s">
+        <v>293</v>
+      </c>
+      <c r="K33" t="s">
         <v>51</v>
       </c>
-      <c r="K33" t="s">
-        <v>263</v>
-      </c>
       <c r="L33" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="N33" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="O33" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
@@ -4463,46 +4784,46 @@
         <v>15</v>
       </c>
       <c r="B34" t="s">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="C34" t="s">
-        <v>249</v>
+        <v>299</v>
       </c>
       <c r="D34">
-        <v>249</v>
+        <v>466</v>
       </c>
       <c r="E34">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F34" t="s">
-        <v>268</v>
+        <v>300</v>
       </c>
       <c r="G34" t="s">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="H34" t="s">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="I34" t="s">
-        <v>271</v>
+        <v>303</v>
       </c>
       <c r="J34" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
       <c r="K34" t="s">
-        <v>273</v>
+        <v>305</v>
       </c>
       <c r="L34" t="s">
-        <v>274</v>
+        <v>306</v>
       </c>
       <c r="M34" t="s">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="N34" t="s">
-        <v>276</v>
+        <v>308</v>
       </c>
       <c r="O34" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
@@ -4510,46 +4831,46 @@
         <v>15</v>
       </c>
       <c r="B35" t="s">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="C35" t="s">
-        <v>249</v>
+        <v>299</v>
       </c>
       <c r="D35">
-        <v>249</v>
+        <v>466</v>
       </c>
       <c r="E35">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F35" t="s">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="G35" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="H35" t="s">
-        <v>280</v>
+        <v>312</v>
       </c>
       <c r="I35" t="s">
-        <v>281</v>
+        <v>313</v>
       </c>
       <c r="J35" t="s">
-        <v>282</v>
+        <v>314</v>
       </c>
       <c r="K35" t="s">
-        <v>283</v>
+        <v>315</v>
       </c>
       <c r="L35" t="s">
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="M35" t="s">
-        <v>285</v>
+        <v>317</v>
       </c>
       <c r="N35" t="s">
-        <v>286</v>
+        <v>318</v>
       </c>
       <c r="O35" t="s">
-        <v>287</v>
+        <v>319</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
@@ -4557,46 +4878,46 @@
         <v>15</v>
       </c>
       <c r="B36" t="s">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="C36" t="s">
-        <v>249</v>
+        <v>299</v>
       </c>
       <c r="D36">
-        <v>249</v>
+        <v>466</v>
       </c>
       <c r="E36">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F36" t="s">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="G36" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="H36" t="s">
-        <v>290</v>
+        <v>322</v>
       </c>
       <c r="I36" t="s">
-        <v>291</v>
+        <v>323</v>
       </c>
       <c r="J36" t="s">
-        <v>292</v>
+        <v>324</v>
       </c>
       <c r="K36" t="s">
-        <v>51</v>
+        <v>325</v>
       </c>
       <c r="L36" t="s">
-        <v>293</v>
+        <v>326</v>
       </c>
       <c r="M36" t="s">
-        <v>294</v>
+        <v>327</v>
       </c>
       <c r="N36" t="s">
-        <v>295</v>
+        <v>328</v>
       </c>
       <c r="O36" t="s">
-        <v>296</v>
+        <v>329</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
@@ -4604,46 +4925,46 @@
         <v>15</v>
       </c>
       <c r="B37" t="s">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="C37" t="s">
-        <v>249</v>
+        <v>299</v>
       </c>
       <c r="D37">
-        <v>249</v>
+        <v>466</v>
       </c>
       <c r="E37">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F37" t="s">
-        <v>297</v>
+        <v>330</v>
       </c>
       <c r="G37" t="s">
-        <v>298</v>
+        <v>331</v>
       </c>
       <c r="H37" t="s">
-        <v>299</v>
+        <v>332</v>
       </c>
       <c r="I37" t="s">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="J37" t="s">
-        <v>301</v>
+        <v>334</v>
       </c>
       <c r="K37" t="s">
-        <v>302</v>
+        <v>335</v>
       </c>
       <c r="L37" t="s">
-        <v>303</v>
+        <v>336</v>
       </c>
       <c r="M37" t="s">
-        <v>304</v>
+        <v>337</v>
       </c>
       <c r="N37" t="s">
-        <v>305</v>
+        <v>338</v>
       </c>
       <c r="O37" t="s">
-        <v>306</v>
+        <v>339</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
@@ -4651,1315 +4972,657 @@
         <v>15</v>
       </c>
       <c r="B38" t="s">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="C38" t="s">
-        <v>249</v>
+        <v>299</v>
       </c>
       <c r="D38">
-        <v>249</v>
+        <v>466</v>
       </c>
       <c r="E38">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F38" t="s">
-        <v>307</v>
+        <v>340</v>
       </c>
       <c r="G38" t="s">
-        <v>308</v>
+        <v>341</v>
       </c>
       <c r="H38" t="s">
-        <v>309</v>
+        <v>342</v>
       </c>
       <c r="I38" t="s">
-        <v>310</v>
+        <v>343</v>
       </c>
       <c r="J38" t="s">
-        <v>311</v>
+        <v>344</v>
       </c>
       <c r="K38" t="s">
-        <v>312</v>
+        <v>345</v>
       </c>
       <c r="L38" t="s">
-        <v>313</v>
+        <v>346</v>
       </c>
       <c r="M38" t="s">
-        <v>314</v>
+        <v>347</v>
       </c>
       <c r="N38" t="s">
-        <v>315</v>
+        <v>348</v>
       </c>
       <c r="O38" t="s">
-        <v>316</v>
+        <v>349</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>15</v>
+        <v>350</v>
       </c>
       <c r="B39" t="s">
-        <v>248</v>
+        <v>351</v>
       </c>
       <c r="C39" t="s">
-        <v>249</v>
+        <v>352</v>
       </c>
       <c r="D39">
-        <v>249</v>
+        <v>46</v>
       </c>
       <c r="E39">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="F39" t="s">
-        <v>317</v>
+        <v>353</v>
       </c>
       <c r="G39" t="s">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="H39" t="s">
-        <v>319</v>
+        <v>355</v>
       </c>
       <c r="I39" t="s">
-        <v>320</v>
+        <v>356</v>
       </c>
       <c r="J39" t="s">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="K39" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="L39" t="s">
-        <v>323</v>
+        <v>359</v>
       </c>
       <c r="M39" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="N39" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="O39" t="s">
-        <v>326</v>
+        <v>362</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>15</v>
+        <v>350</v>
       </c>
       <c r="B40" t="s">
-        <v>248</v>
+        <v>351</v>
       </c>
       <c r="C40" t="s">
-        <v>249</v>
+        <v>352</v>
       </c>
       <c r="D40">
-        <v>249</v>
+        <v>46</v>
       </c>
       <c r="E40">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="F40" t="s">
-        <v>327</v>
+        <v>363</v>
       </c>
       <c r="G40" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="H40" t="s">
-        <v>329</v>
+        <v>365</v>
       </c>
       <c r="I40" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="J40" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="K40" t="s">
-        <v>51</v>
+        <v>368</v>
       </c>
       <c r="L40" t="s">
-        <v>332</v>
+        <v>369</v>
       </c>
       <c r="M40" t="s">
-        <v>333</v>
+        <v>370</v>
       </c>
       <c r="N40" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="O40" t="s">
-        <v>335</v>
+        <v>372</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>15</v>
+        <v>350</v>
       </c>
       <c r="B41" t="s">
-        <v>248</v>
+        <v>351</v>
       </c>
       <c r="C41" t="s">
-        <v>249</v>
+        <v>352</v>
       </c>
       <c r="D41">
-        <v>249</v>
+        <v>46</v>
       </c>
       <c r="E41">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="F41" t="s">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="G41" t="s">
-        <v>337</v>
+        <v>374</v>
       </c>
       <c r="H41" t="s">
-        <v>338</v>
+        <v>375</v>
       </c>
       <c r="I41" t="s">
-        <v>339</v>
+        <v>376</v>
       </c>
       <c r="J41" t="s">
-        <v>340</v>
+        <v>377</v>
       </c>
       <c r="K41" t="s">
-        <v>341</v>
+        <v>378</v>
       </c>
       <c r="L41" t="s">
-        <v>342</v>
+        <v>379</v>
       </c>
       <c r="M41" t="s">
-        <v>343</v>
+        <v>380</v>
       </c>
       <c r="N41" t="s">
-        <v>344</v>
+        <v>381</v>
       </c>
       <c r="O41" t="s">
-        <v>345</v>
+        <v>382</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>15</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C42" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="D42">
-        <v>254</v>
+        <v>46</v>
       </c>
       <c r="E42">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="F42" t="s">
-        <v>348</v>
+        <v>383</v>
       </c>
       <c r="G42" t="s">
-        <v>349</v>
+        <v>384</v>
       </c>
       <c r="H42" t="s">
-        <v>350</v>
+        <v>385</v>
       </c>
       <c r="I42" t="s">
-        <v>351</v>
+        <v>386</v>
       </c>
       <c r="J42" t="s">
-        <v>51</v>
+        <v>387</v>
       </c>
       <c r="K42" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="L42" t="s">
-        <v>353</v>
+        <v>389</v>
       </c>
       <c r="M42" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="N42" t="s">
-        <v>355</v>
+        <v>391</v>
       </c>
       <c r="O42" t="s">
-        <v>356</v>
+        <v>392</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>15</v>
+        <v>350</v>
       </c>
       <c r="B43" t="s">
-        <v>346</v>
+        <v>393</v>
       </c>
       <c r="C43" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="D43">
-        <v>254</v>
+        <v>73</v>
       </c>
       <c r="E43">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="F43" t="s">
-        <v>357</v>
+        <v>395</v>
       </c>
       <c r="G43" t="s">
-        <v>358</v>
+        <v>396</v>
       </c>
       <c r="H43" t="s">
-        <v>359</v>
+        <v>397</v>
       </c>
       <c r="I43" t="s">
-        <v>360</v>
+        <v>398</v>
       </c>
       <c r="J43" t="s">
-        <v>361</v>
+        <v>399</v>
       </c>
       <c r="K43" t="s">
-        <v>362</v>
+        <v>400</v>
       </c>
       <c r="L43" t="s">
-        <v>363</v>
+        <v>401</v>
       </c>
       <c r="M43" t="s">
-        <v>364</v>
+        <v>402</v>
       </c>
       <c r="N43" t="s">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="O43" t="s">
-        <v>366</v>
+        <v>404</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>15</v>
+        <v>350</v>
       </c>
       <c r="B44" t="s">
-        <v>346</v>
+        <v>393</v>
       </c>
       <c r="C44" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="D44">
-        <v>254</v>
+        <v>73</v>
       </c>
       <c r="E44">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="F44" t="s">
-        <v>367</v>
+        <v>405</v>
       </c>
       <c r="G44" t="s">
-        <v>368</v>
+        <v>406</v>
       </c>
       <c r="H44" t="s">
-        <v>369</v>
+        <v>407</v>
       </c>
       <c r="I44" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="J44" t="s">
-        <v>361</v>
+        <v>409</v>
       </c>
       <c r="K44" t="s">
-        <v>371</v>
+        <v>410</v>
       </c>
       <c r="L44" t="s">
-        <v>372</v>
+        <v>411</v>
       </c>
       <c r="M44" t="s">
-        <v>373</v>
+        <v>412</v>
       </c>
       <c r="N44" t="s">
-        <v>374</v>
+        <v>413</v>
       </c>
       <c r="O44" t="s">
-        <v>375</v>
+        <v>414</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>15</v>
+        <v>350</v>
       </c>
       <c r="B45" t="s">
-        <v>346</v>
+        <v>393</v>
       </c>
       <c r="C45" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="D45">
-        <v>254</v>
+        <v>73</v>
       </c>
       <c r="E45">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="F45" t="s">
-        <v>376</v>
+        <v>415</v>
       </c>
       <c r="G45" t="s">
-        <v>377</v>
+        <v>416</v>
       </c>
       <c r="H45" t="s">
-        <v>378</v>
+        <v>417</v>
       </c>
       <c r="I45" t="s">
-        <v>379</v>
+        <v>418</v>
       </c>
       <c r="J45" t="s">
-        <v>51</v>
+        <v>419</v>
       </c>
       <c r="K45" t="s">
-        <v>380</v>
+        <v>420</v>
       </c>
       <c r="L45" t="s">
-        <v>381</v>
+        <v>421</v>
       </c>
       <c r="M45" t="s">
-        <v>382</v>
+        <v>422</v>
       </c>
       <c r="N45" t="s">
-        <v>383</v>
+        <v>423</v>
       </c>
       <c r="O45" t="s">
-        <v>384</v>
+        <v>424</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>15</v>
+        <v>350</v>
       </c>
       <c r="B46" t="s">
-        <v>346</v>
+        <v>393</v>
       </c>
       <c r="C46" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="D46">
-        <v>254</v>
+        <v>73</v>
       </c>
       <c r="E46">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="F46" t="s">
-        <v>348</v>
+        <v>425</v>
       </c>
       <c r="G46" t="s">
-        <v>349</v>
+        <v>426</v>
       </c>
       <c r="H46" t="s">
-        <v>350</v>
+        <v>427</v>
       </c>
       <c r="I46" t="s">
-        <v>351</v>
+        <v>428</v>
       </c>
       <c r="J46" t="s">
+        <v>429</v>
+      </c>
+      <c r="K46" t="s">
         <v>51</v>
       </c>
-      <c r="K46" t="s">
-        <v>352</v>
-      </c>
       <c r="L46" t="s">
-        <v>353</v>
+        <v>430</v>
       </c>
       <c r="M46" t="s">
-        <v>354</v>
+        <v>431</v>
       </c>
       <c r="N46" t="s">
-        <v>355</v>
+        <v>432</v>
       </c>
       <c r="O46" t="s">
-        <v>356</v>
+        <v>433</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>15</v>
+        <v>350</v>
       </c>
       <c r="B47" t="s">
-        <v>346</v>
+        <v>434</v>
       </c>
       <c r="C47" t="s">
-        <v>347</v>
+        <v>435</v>
       </c>
       <c r="D47">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="E47">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F47" t="s">
-        <v>357</v>
+        <v>436</v>
       </c>
       <c r="G47" t="s">
-        <v>358</v>
+        <v>437</v>
       </c>
       <c r="H47" t="s">
-        <v>359</v>
+        <v>438</v>
       </c>
       <c r="I47" t="s">
-        <v>360</v>
+        <v>439</v>
       </c>
       <c r="J47" t="s">
-        <v>361</v>
+        <v>440</v>
       </c>
       <c r="K47" t="s">
-        <v>362</v>
+        <v>441</v>
       </c>
       <c r="L47" t="s">
-        <v>363</v>
+        <v>442</v>
       </c>
       <c r="M47" t="s">
-        <v>364</v>
+        <v>443</v>
       </c>
       <c r="N47" t="s">
-        <v>365</v>
+        <v>444</v>
       </c>
       <c r="O47" t="s">
-        <v>366</v>
+        <v>445</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>15</v>
+        <v>350</v>
       </c>
       <c r="B48" t="s">
-        <v>346</v>
+        <v>434</v>
       </c>
       <c r="C48" t="s">
-        <v>347</v>
+        <v>435</v>
       </c>
       <c r="D48">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="E48">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F48" t="s">
-        <v>367</v>
+        <v>446</v>
       </c>
       <c r="G48" t="s">
-        <v>368</v>
+        <v>447</v>
       </c>
       <c r="H48" t="s">
-        <v>369</v>
+        <v>448</v>
       </c>
       <c r="I48" t="s">
-        <v>370</v>
+        <v>449</v>
       </c>
       <c r="J48" t="s">
-        <v>361</v>
+        <v>450</v>
       </c>
       <c r="K48" t="s">
-        <v>371</v>
+        <v>51</v>
       </c>
       <c r="L48" t="s">
-        <v>372</v>
+        <v>451</v>
       </c>
       <c r="M48" t="s">
-        <v>373</v>
+        <v>452</v>
       </c>
       <c r="N48" t="s">
-        <v>374</v>
+        <v>453</v>
       </c>
       <c r="O48" t="s">
-        <v>375</v>
+        <v>454</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>15</v>
+        <v>350</v>
       </c>
       <c r="B49" t="s">
-        <v>346</v>
+        <v>434</v>
       </c>
       <c r="C49" t="s">
-        <v>347</v>
+        <v>435</v>
       </c>
       <c r="D49">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="E49">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F49" t="s">
-        <v>376</v>
+        <v>455</v>
       </c>
       <c r="G49" t="s">
-        <v>377</v>
+        <v>456</v>
       </c>
       <c r="H49" t="s">
-        <v>378</v>
+        <v>457</v>
       </c>
       <c r="I49" t="s">
-        <v>379</v>
+        <v>458</v>
       </c>
       <c r="J49" t="s">
-        <v>51</v>
+        <v>459</v>
       </c>
       <c r="K49" t="s">
-        <v>380</v>
+        <v>460</v>
       </c>
       <c r="L49" t="s">
-        <v>381</v>
+        <v>461</v>
       </c>
       <c r="M49" t="s">
-        <v>382</v>
+        <v>462</v>
       </c>
       <c r="N49" t="s">
-        <v>383</v>
+        <v>463</v>
       </c>
       <c r="O49" t="s">
-        <v>384</v>
+        <v>464</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>385</v>
+        <v>350</v>
       </c>
       <c r="B50" t="s">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="C50" t="s">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="D50">
-        <v>46</v>
+        <v>226</v>
       </c>
       <c r="E50">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="F50" t="s">
-        <v>388</v>
+        <v>465</v>
       </c>
       <c r="G50" t="s">
-        <v>389</v>
+        <v>466</v>
       </c>
       <c r="H50" t="s">
-        <v>390</v>
+        <v>467</v>
       </c>
       <c r="I50" t="s">
-        <v>391</v>
+        <v>468</v>
       </c>
       <c r="J50" t="s">
-        <v>392</v>
+        <v>469</v>
       </c>
       <c r="K50" t="s">
-        <v>393</v>
+        <v>470</v>
       </c>
       <c r="L50" t="s">
-        <v>394</v>
+        <v>471</v>
       </c>
       <c r="M50" t="s">
-        <v>395</v>
+        <v>472</v>
       </c>
       <c r="N50" t="s">
-        <v>396</v>
+        <v>473</v>
       </c>
       <c r="O50" t="s">
-        <v>397</v>
+        <v>474</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>385</v>
+        <v>350</v>
       </c>
       <c r="B51" t="s">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="C51" t="s">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="D51">
-        <v>46</v>
+        <v>226</v>
       </c>
       <c r="E51">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="F51" t="s">
-        <v>398</v>
+        <v>475</v>
       </c>
       <c r="G51" t="s">
-        <v>399</v>
+        <v>476</v>
       </c>
       <c r="H51" t="s">
-        <v>400</v>
+        <v>477</v>
       </c>
       <c r="I51" t="s">
-        <v>401</v>
+        <v>458</v>
       </c>
       <c r="J51" t="s">
-        <v>402</v>
+        <v>459</v>
       </c>
       <c r="K51" t="s">
-        <v>403</v>
+        <v>478</v>
       </c>
       <c r="L51" t="s">
-        <v>404</v>
+        <v>479</v>
       </c>
       <c r="M51" t="s">
-        <v>405</v>
+        <v>480</v>
       </c>
       <c r="N51" t="s">
-        <v>406</v>
+        <v>481</v>
       </c>
       <c r="O51" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>385</v>
-      </c>
-      <c r="B52" t="s">
-        <v>386</v>
-      </c>
-      <c r="C52" t="s">
-        <v>387</v>
-      </c>
-      <c r="D52">
-        <v>46</v>
-      </c>
-      <c r="E52">
-        <v>24</v>
-      </c>
-      <c r="F52" t="s">
-        <v>408</v>
-      </c>
-      <c r="G52" t="s">
-        <v>409</v>
-      </c>
-      <c r="H52" t="s">
-        <v>410</v>
-      </c>
-      <c r="I52" t="s">
-        <v>411</v>
-      </c>
-      <c r="J52" t="s">
-        <v>412</v>
-      </c>
-      <c r="K52" t="s">
-        <v>413</v>
-      </c>
-      <c r="L52" t="s">
-        <v>414</v>
-      </c>
-      <c r="M52" t="s">
-        <v>415</v>
-      </c>
-      <c r="N52" t="s">
-        <v>416</v>
-      </c>
-      <c r="O52" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>385</v>
-      </c>
-      <c r="B53" t="s">
-        <v>386</v>
-      </c>
-      <c r="C53" t="s">
-        <v>387</v>
-      </c>
-      <c r="D53">
-        <v>46</v>
-      </c>
-      <c r="E53">
-        <v>24</v>
-      </c>
-      <c r="F53" t="s">
-        <v>418</v>
-      </c>
-      <c r="G53" t="s">
-        <v>419</v>
-      </c>
-      <c r="H53" t="s">
-        <v>420</v>
-      </c>
-      <c r="I53" t="s">
-        <v>421</v>
-      </c>
-      <c r="J53" t="s">
-        <v>422</v>
-      </c>
-      <c r="K53" t="s">
-        <v>423</v>
-      </c>
-      <c r="L53" t="s">
-        <v>424</v>
-      </c>
-      <c r="M53" t="s">
-        <v>425</v>
-      </c>
-      <c r="N53" t="s">
-        <v>426</v>
-      </c>
-      <c r="O53" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>385</v>
-      </c>
-      <c r="B54" t="s">
-        <v>386</v>
-      </c>
-      <c r="C54" t="s">
-        <v>387</v>
-      </c>
-      <c r="D54">
-        <v>46</v>
-      </c>
-      <c r="E54">
-        <v>24</v>
-      </c>
-      <c r="F54" t="s">
-        <v>388</v>
-      </c>
-      <c r="G54" t="s">
-        <v>389</v>
-      </c>
-      <c r="H54" t="s">
-        <v>390</v>
-      </c>
-      <c r="I54" t="s">
-        <v>391</v>
-      </c>
-      <c r="J54" t="s">
-        <v>392</v>
-      </c>
-      <c r="K54" t="s">
-        <v>393</v>
-      </c>
-      <c r="L54" t="s">
-        <v>394</v>
-      </c>
-      <c r="M54" t="s">
-        <v>395</v>
-      </c>
-      <c r="N54" t="s">
-        <v>396</v>
-      </c>
-      <c r="O54" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>385</v>
-      </c>
-      <c r="B55" t="s">
-        <v>386</v>
-      </c>
-      <c r="C55" t="s">
-        <v>387</v>
-      </c>
-      <c r="D55">
-        <v>46</v>
-      </c>
-      <c r="E55">
-        <v>24</v>
-      </c>
-      <c r="F55" t="s">
-        <v>398</v>
-      </c>
-      <c r="G55" t="s">
-        <v>399</v>
-      </c>
-      <c r="H55" t="s">
-        <v>400</v>
-      </c>
-      <c r="I55" t="s">
-        <v>401</v>
-      </c>
-      <c r="J55" t="s">
-        <v>402</v>
-      </c>
-      <c r="K55" t="s">
-        <v>403</v>
-      </c>
-      <c r="L55" t="s">
-        <v>404</v>
-      </c>
-      <c r="M55" t="s">
-        <v>405</v>
-      </c>
-      <c r="N55" t="s">
-        <v>406</v>
-      </c>
-      <c r="O55" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>385</v>
-      </c>
-      <c r="B56" t="s">
-        <v>386</v>
-      </c>
-      <c r="C56" t="s">
-        <v>387</v>
-      </c>
-      <c r="D56">
-        <v>46</v>
-      </c>
-      <c r="E56">
-        <v>24</v>
-      </c>
-      <c r="F56" t="s">
-        <v>408</v>
-      </c>
-      <c r="G56" t="s">
-        <v>409</v>
-      </c>
-      <c r="H56" t="s">
-        <v>410</v>
-      </c>
-      <c r="I56" t="s">
-        <v>411</v>
-      </c>
-      <c r="J56" t="s">
-        <v>412</v>
-      </c>
-      <c r="K56" t="s">
-        <v>413</v>
-      </c>
-      <c r="L56" t="s">
-        <v>414</v>
-      </c>
-      <c r="M56" t="s">
-        <v>415</v>
-      </c>
-      <c r="N56" t="s">
-        <v>416</v>
-      </c>
-      <c r="O56" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>385</v>
-      </c>
-      <c r="B57" t="s">
-        <v>386</v>
-      </c>
-      <c r="C57" t="s">
-        <v>387</v>
-      </c>
-      <c r="D57">
-        <v>46</v>
-      </c>
-      <c r="E57">
-        <v>24</v>
-      </c>
-      <c r="F57" t="s">
-        <v>418</v>
-      </c>
-      <c r="G57" t="s">
-        <v>419</v>
-      </c>
-      <c r="H57" t="s">
-        <v>420</v>
-      </c>
-      <c r="I57" t="s">
-        <v>421</v>
-      </c>
-      <c r="J57" t="s">
-        <v>422</v>
-      </c>
-      <c r="K57" t="s">
-        <v>423</v>
-      </c>
-      <c r="L57" t="s">
-        <v>424</v>
-      </c>
-      <c r="M57" t="s">
-        <v>425</v>
-      </c>
-      <c r="N57" t="s">
-        <v>426</v>
-      </c>
-      <c r="O57" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>385</v>
-      </c>
-      <c r="B58" t="s">
-        <v>428</v>
-      </c>
-      <c r="C58" t="s">
-        <v>429</v>
-      </c>
-      <c r="D58">
-        <v>73</v>
-      </c>
-      <c r="E58">
-        <v>22</v>
-      </c>
-      <c r="F58" t="s">
-        <v>430</v>
-      </c>
-      <c r="G58" t="s">
-        <v>431</v>
-      </c>
-      <c r="H58" t="s">
-        <v>432</v>
-      </c>
-      <c r="I58" t="s">
-        <v>433</v>
-      </c>
-      <c r="J58" t="s">
-        <v>434</v>
-      </c>
-      <c r="K58" t="s">
-        <v>435</v>
-      </c>
-      <c r="L58" t="s">
-        <v>436</v>
-      </c>
-      <c r="M58" t="s">
-        <v>437</v>
-      </c>
-      <c r="N58" t="s">
-        <v>438</v>
-      </c>
-      <c r="O58" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>385</v>
-      </c>
-      <c r="B59" t="s">
-        <v>428</v>
-      </c>
-      <c r="C59" t="s">
-        <v>429</v>
-      </c>
-      <c r="D59">
-        <v>73</v>
-      </c>
-      <c r="E59">
-        <v>22</v>
-      </c>
-      <c r="F59" t="s">
-        <v>440</v>
-      </c>
-      <c r="G59" t="s">
-        <v>441</v>
-      </c>
-      <c r="H59" t="s">
-        <v>442</v>
-      </c>
-      <c r="I59" t="s">
-        <v>443</v>
-      </c>
-      <c r="J59" t="s">
-        <v>444</v>
-      </c>
-      <c r="K59" t="s">
-        <v>445</v>
-      </c>
-      <c r="L59" t="s">
-        <v>446</v>
-      </c>
-      <c r="M59" t="s">
-        <v>447</v>
-      </c>
-      <c r="N59" t="s">
-        <v>448</v>
-      </c>
-      <c r="O59" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>385</v>
-      </c>
-      <c r="B60" t="s">
-        <v>428</v>
-      </c>
-      <c r="C60" t="s">
-        <v>429</v>
-      </c>
-      <c r="D60">
-        <v>73</v>
-      </c>
-      <c r="E60">
-        <v>22</v>
-      </c>
-      <c r="F60" t="s">
-        <v>450</v>
-      </c>
-      <c r="G60" t="s">
-        <v>451</v>
-      </c>
-      <c r="H60" t="s">
-        <v>452</v>
-      </c>
-      <c r="I60" t="s">
-        <v>453</v>
-      </c>
-      <c r="J60" t="s">
-        <v>454</v>
-      </c>
-      <c r="K60" t="s">
-        <v>455</v>
-      </c>
-      <c r="L60" t="s">
-        <v>456</v>
-      </c>
-      <c r="M60" t="s">
-        <v>457</v>
-      </c>
-      <c r="N60" t="s">
-        <v>458</v>
-      </c>
-      <c r="O60" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>385</v>
-      </c>
-      <c r="B61" t="s">
-        <v>428</v>
-      </c>
-      <c r="C61" t="s">
-        <v>429</v>
-      </c>
-      <c r="D61">
-        <v>73</v>
-      </c>
-      <c r="E61">
-        <v>22</v>
-      </c>
-      <c r="F61" t="s">
-        <v>460</v>
-      </c>
-      <c r="G61" t="s">
-        <v>461</v>
-      </c>
-      <c r="H61" t="s">
-        <v>462</v>
-      </c>
-      <c r="I61" t="s">
-        <v>463</v>
-      </c>
-      <c r="J61" t="s">
-        <v>464</v>
-      </c>
-      <c r="K61" t="s">
-        <v>51</v>
-      </c>
-      <c r="L61" t="s">
-        <v>465</v>
-      </c>
-      <c r="M61" t="s">
-        <v>466</v>
-      </c>
-      <c r="N61" t="s">
-        <v>467</v>
-      </c>
-      <c r="O61" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>385</v>
-      </c>
-      <c r="B62" t="s">
-        <v>428</v>
-      </c>
-      <c r="C62" t="s">
-        <v>429</v>
-      </c>
-      <c r="D62">
-        <v>73</v>
-      </c>
-      <c r="E62">
-        <v>22</v>
-      </c>
-      <c r="F62" t="s">
-        <v>430</v>
-      </c>
-      <c r="G62" t="s">
-        <v>431</v>
-      </c>
-      <c r="H62" t="s">
-        <v>432</v>
-      </c>
-      <c r="I62" t="s">
-        <v>433</v>
-      </c>
-      <c r="J62" t="s">
-        <v>434</v>
-      </c>
-      <c r="K62" t="s">
-        <v>435</v>
-      </c>
-      <c r="L62" t="s">
-        <v>436</v>
-      </c>
-      <c r="M62" t="s">
-        <v>437</v>
-      </c>
-      <c r="N62" t="s">
-        <v>438</v>
-      </c>
-      <c r="O62" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>385</v>
-      </c>
-      <c r="B63" t="s">
-        <v>428</v>
-      </c>
-      <c r="C63" t="s">
-        <v>429</v>
-      </c>
-      <c r="D63">
-        <v>73</v>
-      </c>
-      <c r="E63">
-        <v>22</v>
-      </c>
-      <c r="F63" t="s">
-        <v>440</v>
-      </c>
-      <c r="G63" t="s">
-        <v>441</v>
-      </c>
-      <c r="H63" t="s">
-        <v>442</v>
-      </c>
-      <c r="I63" t="s">
-        <v>443</v>
-      </c>
-      <c r="J63" t="s">
-        <v>444</v>
-      </c>
-      <c r="K63" t="s">
-        <v>445</v>
-      </c>
-      <c r="L63" t="s">
-        <v>446</v>
-      </c>
-      <c r="M63" t="s">
-        <v>447</v>
-      </c>
-      <c r="N63" t="s">
-        <v>448</v>
-      </c>
-      <c r="O63" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>385</v>
-      </c>
-      <c r="B64" t="s">
-        <v>428</v>
-      </c>
-      <c r="C64" t="s">
-        <v>429</v>
-      </c>
-      <c r="D64">
-        <v>73</v>
-      </c>
-      <c r="E64">
-        <v>22</v>
-      </c>
-      <c r="F64" t="s">
-        <v>450</v>
-      </c>
-      <c r="G64" t="s">
-        <v>451</v>
-      </c>
-      <c r="H64" t="s">
-        <v>452</v>
-      </c>
-      <c r="I64" t="s">
-        <v>453</v>
-      </c>
-      <c r="J64" t="s">
-        <v>454</v>
-      </c>
-      <c r="K64" t="s">
-        <v>455</v>
-      </c>
-      <c r="L64" t="s">
-        <v>456</v>
-      </c>
-      <c r="M64" t="s">
-        <v>457</v>
-      </c>
-      <c r="N64" t="s">
-        <v>458</v>
-      </c>
-      <c r="O64" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>385</v>
-      </c>
-      <c r="B65" t="s">
-        <v>428</v>
-      </c>
-      <c r="C65" t="s">
-        <v>429</v>
-      </c>
-      <c r="D65">
-        <v>73</v>
-      </c>
-      <c r="E65">
-        <v>22</v>
-      </c>
-      <c r="F65" t="s">
-        <v>460</v>
-      </c>
-      <c r="G65" t="s">
-        <v>461</v>
-      </c>
-      <c r="H65" t="s">
-        <v>462</v>
-      </c>
-      <c r="I65" t="s">
-        <v>463</v>
-      </c>
-      <c r="J65" t="s">
-        <v>464</v>
-      </c>
-      <c r="K65" t="s">
-        <v>51</v>
-      </c>
-      <c r="L65" t="s">
-        <v>465</v>
-      </c>
-      <c r="M65" t="s">
-        <v>466</v>
-      </c>
-      <c r="N65" t="s">
-        <v>467</v>
-      </c>
-      <c r="O65" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
